--- a/01.Documentation/01.Diseño/Calibracion DAC.xlsx
+++ b/01.Documentation/01.Diseño/Calibracion DAC.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Team Dropbox\JRODRIGUEZ\Repositorios\01.Rover\01.Documentation\01.Diseño\Tests\DCDC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Team Dropbox\JRODRIGUEZ\Repositorios\01.Rover\01.Documentation\01.Diseño\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E91FEC0-ABBB-49CB-9AB1-AF4248C20212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29F89DD-081B-4415-B3A2-22DAFD77D9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2295" yWindow="2295" windowWidth="21600" windowHeight="11295" activeTab="3" xr2:uid="{1F2CF652-4A2E-4701-B4BE-D2C83886312B}"/>
+    <workbookView minimized="1" xWindow="-25290" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{1F2CF652-4A2E-4701-B4BE-D2C83886312B}"/>
   </bookViews>
   <sheets>
     <sheet name="120-1420" sheetId="1" r:id="rId1"/>
     <sheet name="140-1435" sheetId="2" r:id="rId2"/>
     <sheet name="Tarjeta verificacion" sheetId="3" r:id="rId3"/>
     <sheet name="140-1435 (2)" sheetId="4" r:id="rId4"/>
+    <sheet name="140-1435 (3)" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" iterate="1"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="20">
   <si>
     <t>DAC count</t>
   </si>
@@ -2193,6 +2194,1961 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-4E55-45BC-9030-702BB93415A9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1955612608"/>
+        <c:axId val="1955616352"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1955612608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1955616352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1955616352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1955612608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'140-1435 (3)'!$D$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vout teorico
+(mV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'140-1435 (3)'!$D$7:$D$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5200</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5400</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5600</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6200</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6400</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6600</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7400</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7600</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8200</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8400</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8600</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9200</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9400</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9600</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9800</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9900</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>10100</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>10300</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>10400</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>10500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>10600</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>10700</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10800</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5523-473D-AA35-E40F1B977152}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'140-1435 (3)'!$E$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vout medido
+(mV) </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>'140-1435 (3)'!$E$7:$E$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-5523-473D-AA35-E40F1B977152}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1693085360"/>
+        <c:axId val="1693088272"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1693085360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1693088272"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1693088272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="13000"/>
+          <c:min val="4000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1693085360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'140-1435 (3)'!$F$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Error(mV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'140-1435 (3)'!$D$7:$D$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5200</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5400</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5600</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6200</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6400</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6600</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7400</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7600</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8200</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8400</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8600</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9200</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9400</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9600</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9800</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9900</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>10100</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>10300</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>10400</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>10500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>10600</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>10700</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10800</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'140-1435 (3)'!$F$7:$F$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>-4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-5100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5200</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-5300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-5400</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-5500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-5600</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-5700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-5800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-5900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-6000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-6100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-6200</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-6300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-6400</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-6500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-6600</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-6700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-6800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-6900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-7000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-7100</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-7200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-7300</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-7400</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-7500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-7600</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-7700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-7800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-8000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-8100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-8200</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-8300</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-8400</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-8500</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-8600</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-8700</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-8800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-8900</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-9000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-9100</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-9200</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-9300</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-9400</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-9500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-9600</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-9700</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-9800</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-9900</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-10000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-10100</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-10200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-10300</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-10400</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-10500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-10600</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-10700</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-10800</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-10900</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-714C-46F0-BF69-5ED460A232DA}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1959899648"/>
+        <c:axId val="1959900064"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1959899648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="12000"/>
+          <c:min val="5000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1959900064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1959900064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1959899648"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'140-1435 (3)'!$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Err(q)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'140-1435 (3)'!$D$7:$D$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5200</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5400</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5600</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6200</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6400</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6600</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7400</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7600</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8200</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8400</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8600</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9200</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9400</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9600</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9800</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9900</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>10100</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>10300</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>10400</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>10500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>10600</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>10700</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10800</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'140-1435 (3)'!$G$7:$G$77</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>-1365.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1399.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1433.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1467.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1501.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1536</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1570.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1604.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1638.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1672.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1706.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1740.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1774.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1809.1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1843.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1877.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1911.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1945.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1979.7</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-2013.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-2048</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-2082.1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-2116.3000000000002</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-2150.4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-2184.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-2218.6999999999998</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-2252.8000000000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-2286.9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-2321.1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-2355.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-2389.3000000000002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-2423.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-2457.6</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-2491.6999999999998</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-2525.9</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-2560</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-2594.1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-2628.3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-2662.4</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-2696.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-2730.7</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-2764.8</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-2798.9</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-2833.1</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-2867.2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-2901.3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-2935.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-2969.6</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-3003.7</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-3037.9</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-3072</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-3106.1</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-3140.3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-3174.4</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-3208.5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-3242.7</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-3276.8</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-3310.9</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-3345.1</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-3379.2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-3413.3</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-3447.5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-3481.6</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-3515.7</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-3549.9</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-3584</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-3618.1</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-3652.3</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-3686.4</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-3720.5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-3754.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A8B3-4397-96EA-E925A432147C}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8077,6 +10033,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -9430,6 +11506,1541 @@
 </file>
 
 <file path=xl/charts/style11.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style12.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -14464,6 +18075,125 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>71437</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{186AA879-2CC7-45C4-880A-23AB7E89C3F4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D3B60B9-25C8-4A33-B897-63DBAF48CAE3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>33337</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18A4C0B8-B3D5-4E88-94A4-AB391C42F92F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -22541,4 +26271,2043 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E57B80C9-DE72-41F4-850D-88317024A728}">
+  <dimension ref="A1:J87"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1">
+        <v>120</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1">
+        <v>3000</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>45</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1024</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3">
+        <f>E1/E2</f>
+        <v>2.9296875</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>140</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <f>ROUND(B3*E2/E1,0)</f>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>1536</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>ROUND( B4*E2/E1,0)</f>
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>40</v>
+      </c>
+      <c r="B7" s="6">
+        <f t="shared" ref="B7:B70" si="0">ROUND($E$4-(((A7-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
+        <v>556</v>
+      </c>
+      <c r="C7" s="7">
+        <f>B7*$E$1/$E$2</f>
+        <v>1628.90625</v>
+      </c>
+      <c r="D7" s="6">
+        <v>4000</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
+        <f>E7-D7</f>
+        <v>-4000</v>
+      </c>
+      <c r="G7" s="9">
+        <f>ROUND(F7/$I$2,1)</f>
+        <v>-1365.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>41</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>549</v>
+      </c>
+      <c r="C8" s="5">
+        <f>B8*$E$1/$E$2</f>
+        <v>1608.3984375</v>
+      </c>
+      <c r="D8">
+        <v>4100</v>
+      </c>
+      <c r="F8">
+        <f t="shared" ref="F8:F71" si="1">E8-D8</f>
+        <v>-4100</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" ref="G8:G71" si="2">ROUND(F8/$I$2,1)</f>
+        <v>-1399.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>42</v>
+      </c>
+      <c r="B9" s="6">
+        <f t="shared" ref="B9:B72" si="3">ROUND($E$4-(((A9-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
+        <v>543</v>
+      </c>
+      <c r="C9" s="7">
+        <f t="shared" ref="C9:C72" si="4">B9*$E$1/$E$2</f>
+        <v>1590.8203125</v>
+      </c>
+      <c r="D9" s="6">
+        <v>4200</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="1"/>
+        <v>-4200</v>
+      </c>
+      <c r="G9" s="4">
+        <f t="shared" si="2"/>
+        <v>-1433.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>43</v>
+      </c>
+      <c r="B10">
+        <f t="shared" si="3"/>
+        <v>537</v>
+      </c>
+      <c r="C10" s="5">
+        <f t="shared" si="4"/>
+        <v>1573.2421875</v>
+      </c>
+      <c r="D10">
+        <v>4300</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="1"/>
+        <v>-4300</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="2"/>
+        <v>-1467.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>44</v>
+      </c>
+      <c r="B11" s="6">
+        <f t="shared" si="3"/>
+        <v>530</v>
+      </c>
+      <c r="C11" s="7">
+        <f t="shared" si="4"/>
+        <v>1552.734375</v>
+      </c>
+      <c r="D11" s="6">
+        <v>4400</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="1"/>
+        <v>-4400</v>
+      </c>
+      <c r="G11" s="4">
+        <f t="shared" si="2"/>
+        <v>-1501.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>45</v>
+      </c>
+      <c r="B12">
+        <f t="shared" si="3"/>
+        <v>524</v>
+      </c>
+      <c r="C12" s="5">
+        <f t="shared" si="4"/>
+        <v>1535.15625</v>
+      </c>
+      <c r="D12">
+        <v>4500</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="1"/>
+        <v>-4500</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="2"/>
+        <v>-1536</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>46</v>
+      </c>
+      <c r="B13" s="6">
+        <f t="shared" si="3"/>
+        <v>518</v>
+      </c>
+      <c r="C13" s="7">
+        <f t="shared" si="4"/>
+        <v>1517.578125</v>
+      </c>
+      <c r="D13" s="6">
+        <v>4600</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="1"/>
+        <v>-4600</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="2"/>
+        <v>-1570.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>47</v>
+      </c>
+      <c r="B14">
+        <f t="shared" si="3"/>
+        <v>511</v>
+      </c>
+      <c r="C14" s="5">
+        <f t="shared" si="4"/>
+        <v>1497.0703125</v>
+      </c>
+      <c r="D14">
+        <v>4700</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="1"/>
+        <v>-4700</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="2"/>
+        <v>-1604.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>48</v>
+      </c>
+      <c r="B15" s="6">
+        <f t="shared" si="3"/>
+        <v>505</v>
+      </c>
+      <c r="C15" s="7">
+        <f t="shared" si="4"/>
+        <v>1479.4921875</v>
+      </c>
+      <c r="D15" s="6">
+        <v>4800</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="1"/>
+        <v>-4800</v>
+      </c>
+      <c r="G15" s="4">
+        <f t="shared" si="2"/>
+        <v>-1638.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>49</v>
+      </c>
+      <c r="B16">
+        <f t="shared" si="3"/>
+        <v>499</v>
+      </c>
+      <c r="C16" s="5">
+        <f t="shared" si="4"/>
+        <v>1461.9140625</v>
+      </c>
+      <c r="D16">
+        <v>4900</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="1"/>
+        <v>-4900</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="2"/>
+        <v>-1672.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>50</v>
+      </c>
+      <c r="B17" s="6">
+        <f t="shared" si="3"/>
+        <v>492</v>
+      </c>
+      <c r="C17" s="7">
+        <f t="shared" si="4"/>
+        <v>1441.40625</v>
+      </c>
+      <c r="D17" s="6">
+        <v>5000</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6">
+        <f t="shared" si="1"/>
+        <v>-5000</v>
+      </c>
+      <c r="G17" s="9">
+        <f t="shared" si="2"/>
+        <v>-1706.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>51</v>
+      </c>
+      <c r="B18">
+        <f t="shared" si="3"/>
+        <v>486</v>
+      </c>
+      <c r="C18" s="5">
+        <f t="shared" si="4"/>
+        <v>1423.828125</v>
+      </c>
+      <c r="D18">
+        <v>5100</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="1"/>
+        <v>-5100</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="2"/>
+        <v>-1740.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>52</v>
+      </c>
+      <c r="B19" s="6">
+        <f t="shared" si="3"/>
+        <v>480</v>
+      </c>
+      <c r="C19" s="7">
+        <f t="shared" si="4"/>
+        <v>1406.25</v>
+      </c>
+      <c r="D19" s="6">
+        <v>5200</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="1"/>
+        <v>-5200</v>
+      </c>
+      <c r="G19" s="4">
+        <f t="shared" si="2"/>
+        <v>-1774.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>53</v>
+      </c>
+      <c r="B20">
+        <f t="shared" si="3"/>
+        <v>473</v>
+      </c>
+      <c r="C20" s="5">
+        <f t="shared" si="4"/>
+        <v>1385.7421875</v>
+      </c>
+      <c r="D20">
+        <v>5300</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="1"/>
+        <v>-5300</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="2"/>
+        <v>-1809.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>54</v>
+      </c>
+      <c r="B21" s="6">
+        <f t="shared" si="3"/>
+        <v>467</v>
+      </c>
+      <c r="C21" s="7">
+        <f t="shared" si="4"/>
+        <v>1368.1640625</v>
+      </c>
+      <c r="D21" s="6">
+        <v>5400</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="1"/>
+        <v>-5400</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" si="2"/>
+        <v>-1843.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>55</v>
+      </c>
+      <c r="B22">
+        <f t="shared" si="3"/>
+        <v>461</v>
+      </c>
+      <c r="C22" s="5">
+        <f t="shared" si="4"/>
+        <v>1350.5859375</v>
+      </c>
+      <c r="D22">
+        <v>5500</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="1"/>
+        <v>-5500</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="2"/>
+        <v>-1877.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>56</v>
+      </c>
+      <c r="B23" s="6">
+        <f t="shared" si="3"/>
+        <v>454</v>
+      </c>
+      <c r="C23" s="7">
+        <f t="shared" si="4"/>
+        <v>1330.078125</v>
+      </c>
+      <c r="D23" s="6">
+        <v>5600</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="1"/>
+        <v>-5600</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="2"/>
+        <v>-1911.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>57</v>
+      </c>
+      <c r="B24">
+        <f t="shared" si="3"/>
+        <v>448</v>
+      </c>
+      <c r="C24" s="5">
+        <f t="shared" si="4"/>
+        <v>1312.5</v>
+      </c>
+      <c r="D24">
+        <v>5700</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="1"/>
+        <v>-5700</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="2"/>
+        <v>-1945.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>58</v>
+      </c>
+      <c r="B25" s="6">
+        <f t="shared" si="3"/>
+        <v>441</v>
+      </c>
+      <c r="C25" s="7">
+        <f t="shared" si="4"/>
+        <v>1291.9921875</v>
+      </c>
+      <c r="D25" s="6">
+        <v>5800</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="1"/>
+        <v>-5800</v>
+      </c>
+      <c r="G25" s="4">
+        <f t="shared" si="2"/>
+        <v>-1979.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>59</v>
+      </c>
+      <c r="B26">
+        <f t="shared" si="3"/>
+        <v>435</v>
+      </c>
+      <c r="C26" s="5">
+        <f t="shared" si="4"/>
+        <v>1274.4140625</v>
+      </c>
+      <c r="D26">
+        <v>5900</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="1"/>
+        <v>-5900</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="2"/>
+        <v>-2013.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>60</v>
+      </c>
+      <c r="B27" s="6">
+        <f t="shared" si="3"/>
+        <v>429</v>
+      </c>
+      <c r="C27" s="7">
+        <f t="shared" si="4"/>
+        <v>1256.8359375</v>
+      </c>
+      <c r="D27" s="6">
+        <v>6000</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6">
+        <f t="shared" si="1"/>
+        <v>-6000</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="2"/>
+        <v>-2048</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>61</v>
+      </c>
+      <c r="B28">
+        <f t="shared" si="3"/>
+        <v>422</v>
+      </c>
+      <c r="C28" s="5">
+        <f t="shared" si="4"/>
+        <v>1236.328125</v>
+      </c>
+      <c r="D28">
+        <v>6100</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="1"/>
+        <v>-6100</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="2"/>
+        <v>-2082.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>62</v>
+      </c>
+      <c r="B29" s="6">
+        <f t="shared" si="3"/>
+        <v>416</v>
+      </c>
+      <c r="C29" s="7">
+        <f t="shared" si="4"/>
+        <v>1218.75</v>
+      </c>
+      <c r="D29" s="6">
+        <v>6200</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="1"/>
+        <v>-6200</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="2"/>
+        <v>-2116.3000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>63</v>
+      </c>
+      <c r="B30">
+        <f t="shared" si="3"/>
+        <v>410</v>
+      </c>
+      <c r="C30" s="5">
+        <f t="shared" si="4"/>
+        <v>1201.171875</v>
+      </c>
+      <c r="D30">
+        <v>6300</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="1"/>
+        <v>-6300</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="2"/>
+        <v>-2150.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>64</v>
+      </c>
+      <c r="B31" s="6">
+        <f t="shared" si="3"/>
+        <v>403</v>
+      </c>
+      <c r="C31" s="7">
+        <f t="shared" si="4"/>
+        <v>1180.6640625</v>
+      </c>
+      <c r="D31" s="6">
+        <v>6400</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="1"/>
+        <v>-6400</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" si="2"/>
+        <v>-2184.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>65</v>
+      </c>
+      <c r="B32">
+        <f t="shared" si="3"/>
+        <v>397</v>
+      </c>
+      <c r="C32" s="5">
+        <f t="shared" si="4"/>
+        <v>1163.0859375</v>
+      </c>
+      <c r="D32">
+        <v>6500</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="1"/>
+        <v>-6500</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="2"/>
+        <v>-2218.6999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>66</v>
+      </c>
+      <c r="B33" s="6">
+        <f t="shared" si="3"/>
+        <v>391</v>
+      </c>
+      <c r="C33" s="7">
+        <f t="shared" si="4"/>
+        <v>1145.5078125</v>
+      </c>
+      <c r="D33" s="6">
+        <v>6600</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="1"/>
+        <v>-6600</v>
+      </c>
+      <c r="G33" s="4">
+        <f t="shared" si="2"/>
+        <v>-2252.8000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>67</v>
+      </c>
+      <c r="B34">
+        <f t="shared" si="3"/>
+        <v>384</v>
+      </c>
+      <c r="C34" s="5">
+        <f t="shared" si="4"/>
+        <v>1125</v>
+      </c>
+      <c r="D34">
+        <v>6700</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="1"/>
+        <v>-6700</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="2"/>
+        <v>-2286.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>68</v>
+      </c>
+      <c r="B35" s="6">
+        <f t="shared" si="3"/>
+        <v>378</v>
+      </c>
+      <c r="C35" s="7">
+        <f t="shared" si="4"/>
+        <v>1107.421875</v>
+      </c>
+      <c r="D35" s="6">
+        <v>6800</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="1"/>
+        <v>-6800</v>
+      </c>
+      <c r="G35" s="4">
+        <f t="shared" si="2"/>
+        <v>-2321.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>69</v>
+      </c>
+      <c r="B36">
+        <f t="shared" si="3"/>
+        <v>372</v>
+      </c>
+      <c r="C36" s="5">
+        <f t="shared" si="4"/>
+        <v>1089.84375</v>
+      </c>
+      <c r="D36">
+        <v>6900</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="1"/>
+        <v>-6900</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="2"/>
+        <v>-2355.1999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>70</v>
+      </c>
+      <c r="B37" s="6">
+        <f t="shared" si="3"/>
+        <v>365</v>
+      </c>
+      <c r="C37" s="7">
+        <f t="shared" si="4"/>
+        <v>1069.3359375</v>
+      </c>
+      <c r="D37" s="6">
+        <v>7000</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6">
+        <f t="shared" si="1"/>
+        <v>-7000</v>
+      </c>
+      <c r="G37" s="9">
+        <f t="shared" si="2"/>
+        <v>-2389.3000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>71</v>
+      </c>
+      <c r="B38">
+        <f t="shared" si="3"/>
+        <v>359</v>
+      </c>
+      <c r="C38" s="5">
+        <f t="shared" si="4"/>
+        <v>1051.7578125</v>
+      </c>
+      <c r="D38">
+        <v>7100</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="1"/>
+        <v>-7100</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="2"/>
+        <v>-2423.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>72</v>
+      </c>
+      <c r="B39" s="6">
+        <f t="shared" si="3"/>
+        <v>353</v>
+      </c>
+      <c r="C39" s="7">
+        <f t="shared" si="4"/>
+        <v>1034.1796875</v>
+      </c>
+      <c r="D39" s="6">
+        <v>7200</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="1"/>
+        <v>-7200</v>
+      </c>
+      <c r="G39" s="4">
+        <f t="shared" si="2"/>
+        <v>-2457.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>73</v>
+      </c>
+      <c r="B40">
+        <f t="shared" si="3"/>
+        <v>346</v>
+      </c>
+      <c r="C40" s="5">
+        <f t="shared" si="4"/>
+        <v>1013.671875</v>
+      </c>
+      <c r="D40">
+        <v>7300</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="1"/>
+        <v>-7300</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="2"/>
+        <v>-2491.6999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>74</v>
+      </c>
+      <c r="B41" s="6">
+        <f t="shared" si="3"/>
+        <v>340</v>
+      </c>
+      <c r="C41" s="7">
+        <f t="shared" si="4"/>
+        <v>996.09375</v>
+      </c>
+      <c r="D41" s="6">
+        <v>7400</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="1"/>
+        <v>-7400</v>
+      </c>
+      <c r="G41" s="4">
+        <f t="shared" si="2"/>
+        <v>-2525.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>75</v>
+      </c>
+      <c r="B42">
+        <f t="shared" si="3"/>
+        <v>334</v>
+      </c>
+      <c r="C42" s="5">
+        <f t="shared" si="4"/>
+        <v>978.515625</v>
+      </c>
+      <c r="D42">
+        <v>7500</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="1"/>
+        <v>-7500</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="2"/>
+        <v>-2560</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>76</v>
+      </c>
+      <c r="B43" s="6">
+        <f t="shared" si="3"/>
+        <v>327</v>
+      </c>
+      <c r="C43" s="7">
+        <f t="shared" si="4"/>
+        <v>958.0078125</v>
+      </c>
+      <c r="D43" s="6">
+        <v>7600</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="1"/>
+        <v>-7600</v>
+      </c>
+      <c r="G43" s="4">
+        <f t="shared" si="2"/>
+        <v>-2594.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>77</v>
+      </c>
+      <c r="B44">
+        <f t="shared" si="3"/>
+        <v>321</v>
+      </c>
+      <c r="C44" s="5">
+        <f t="shared" si="4"/>
+        <v>940.4296875</v>
+      </c>
+      <c r="D44">
+        <v>7700</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="1"/>
+        <v>-7700</v>
+      </c>
+      <c r="G44" s="4">
+        <f t="shared" si="2"/>
+        <v>-2628.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>78</v>
+      </c>
+      <c r="B45" s="6">
+        <f t="shared" si="3"/>
+        <v>315</v>
+      </c>
+      <c r="C45" s="7">
+        <f t="shared" si="4"/>
+        <v>922.8515625</v>
+      </c>
+      <c r="D45" s="6">
+        <v>7800</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="1"/>
+        <v>-7800</v>
+      </c>
+      <c r="G45" s="4">
+        <f t="shared" si="2"/>
+        <v>-2662.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>79</v>
+      </c>
+      <c r="B46">
+        <f t="shared" si="3"/>
+        <v>308</v>
+      </c>
+      <c r="C46" s="5">
+        <f t="shared" si="4"/>
+        <v>902.34375</v>
+      </c>
+      <c r="D46">
+        <v>7900</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="1"/>
+        <v>-7900</v>
+      </c>
+      <c r="G46" s="4">
+        <f t="shared" si="2"/>
+        <v>-2696.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>80</v>
+      </c>
+      <c r="B47" s="6">
+        <f t="shared" si="3"/>
+        <v>302</v>
+      </c>
+      <c r="C47" s="7">
+        <f t="shared" si="4"/>
+        <v>884.765625</v>
+      </c>
+      <c r="D47" s="6">
+        <v>8000</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6">
+        <f t="shared" si="1"/>
+        <v>-8000</v>
+      </c>
+      <c r="G47" s="9">
+        <f t="shared" si="2"/>
+        <v>-2730.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>81</v>
+      </c>
+      <c r="B48">
+        <f t="shared" si="3"/>
+        <v>296</v>
+      </c>
+      <c r="C48" s="5">
+        <f t="shared" si="4"/>
+        <v>867.1875</v>
+      </c>
+      <c r="D48">
+        <v>8100</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="1"/>
+        <v>-8100</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="2"/>
+        <v>-2764.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>82</v>
+      </c>
+      <c r="B49" s="6">
+        <f t="shared" si="3"/>
+        <v>289</v>
+      </c>
+      <c r="C49" s="7">
+        <f t="shared" si="4"/>
+        <v>846.6796875</v>
+      </c>
+      <c r="D49" s="6">
+        <v>8200</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="1"/>
+        <v>-8200</v>
+      </c>
+      <c r="G49" s="4">
+        <f t="shared" si="2"/>
+        <v>-2798.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>83</v>
+      </c>
+      <c r="B50">
+        <f t="shared" si="3"/>
+        <v>283</v>
+      </c>
+      <c r="C50" s="5">
+        <f t="shared" si="4"/>
+        <v>829.1015625</v>
+      </c>
+      <c r="D50">
+        <v>8300</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="1"/>
+        <v>-8300</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="2"/>
+        <v>-2833.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>84</v>
+      </c>
+      <c r="B51" s="6">
+        <f t="shared" si="3"/>
+        <v>276</v>
+      </c>
+      <c r="C51" s="7">
+        <f t="shared" si="4"/>
+        <v>808.59375</v>
+      </c>
+      <c r="D51" s="6">
+        <v>8400</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="1"/>
+        <v>-8400</v>
+      </c>
+      <c r="G51" s="4">
+        <f t="shared" si="2"/>
+        <v>-2867.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>85</v>
+      </c>
+      <c r="B52">
+        <f t="shared" si="3"/>
+        <v>270</v>
+      </c>
+      <c r="C52" s="5">
+        <f t="shared" si="4"/>
+        <v>791.015625</v>
+      </c>
+      <c r="D52">
+        <v>8500</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="1"/>
+        <v>-8500</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="2"/>
+        <v>-2901.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>86</v>
+      </c>
+      <c r="B53" s="6">
+        <f t="shared" si="3"/>
+        <v>264</v>
+      </c>
+      <c r="C53" s="7">
+        <f t="shared" si="4"/>
+        <v>773.4375</v>
+      </c>
+      <c r="D53" s="6">
+        <v>8600</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="1"/>
+        <v>-8600</v>
+      </c>
+      <c r="G53" s="4">
+        <f t="shared" si="2"/>
+        <v>-2935.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>87</v>
+      </c>
+      <c r="B54">
+        <f t="shared" si="3"/>
+        <v>257</v>
+      </c>
+      <c r="C54" s="5">
+        <f t="shared" si="4"/>
+        <v>752.9296875</v>
+      </c>
+      <c r="D54">
+        <v>8700</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="1"/>
+        <v>-8700</v>
+      </c>
+      <c r="G54" s="4">
+        <f t="shared" si="2"/>
+        <v>-2969.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>88</v>
+      </c>
+      <c r="B55" s="6">
+        <f t="shared" si="3"/>
+        <v>251</v>
+      </c>
+      <c r="C55" s="7">
+        <f t="shared" si="4"/>
+        <v>735.3515625</v>
+      </c>
+      <c r="D55" s="6">
+        <v>8800</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="1"/>
+        <v>-8800</v>
+      </c>
+      <c r="G55" s="4">
+        <f t="shared" si="2"/>
+        <v>-3003.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>89</v>
+      </c>
+      <c r="B56">
+        <f t="shared" si="3"/>
+        <v>245</v>
+      </c>
+      <c r="C56" s="5">
+        <f t="shared" si="4"/>
+        <v>717.7734375</v>
+      </c>
+      <c r="D56">
+        <v>8900</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="1"/>
+        <v>-8900</v>
+      </c>
+      <c r="G56" s="4">
+        <f t="shared" si="2"/>
+        <v>-3037.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>90</v>
+      </c>
+      <c r="B57" s="6">
+        <f t="shared" si="3"/>
+        <v>238</v>
+      </c>
+      <c r="C57" s="7">
+        <f t="shared" si="4"/>
+        <v>697.265625</v>
+      </c>
+      <c r="D57" s="6">
+        <v>9000</v>
+      </c>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6">
+        <f t="shared" si="1"/>
+        <v>-9000</v>
+      </c>
+      <c r="G57" s="9">
+        <f t="shared" si="2"/>
+        <v>-3072</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>91</v>
+      </c>
+      <c r="B58">
+        <f t="shared" si="3"/>
+        <v>232</v>
+      </c>
+      <c r="C58" s="5">
+        <f t="shared" si="4"/>
+        <v>679.6875</v>
+      </c>
+      <c r="D58">
+        <v>9100</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="1"/>
+        <v>-9100</v>
+      </c>
+      <c r="G58" s="4">
+        <f t="shared" si="2"/>
+        <v>-3106.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>92</v>
+      </c>
+      <c r="B59" s="6">
+        <f t="shared" si="3"/>
+        <v>226</v>
+      </c>
+      <c r="C59" s="7">
+        <f t="shared" si="4"/>
+        <v>662.109375</v>
+      </c>
+      <c r="D59" s="6">
+        <v>9200</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="1"/>
+        <v>-9200</v>
+      </c>
+      <c r="G59" s="4">
+        <f t="shared" si="2"/>
+        <v>-3140.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>93</v>
+      </c>
+      <c r="B60">
+        <f t="shared" si="3"/>
+        <v>219</v>
+      </c>
+      <c r="C60" s="5">
+        <f t="shared" si="4"/>
+        <v>641.6015625</v>
+      </c>
+      <c r="D60">
+        <v>9300</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="1"/>
+        <v>-9300</v>
+      </c>
+      <c r="G60" s="4">
+        <f t="shared" si="2"/>
+        <v>-3174.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>94</v>
+      </c>
+      <c r="B61" s="6">
+        <f t="shared" si="3"/>
+        <v>213</v>
+      </c>
+      <c r="C61" s="7">
+        <f t="shared" si="4"/>
+        <v>624.0234375</v>
+      </c>
+      <c r="D61" s="6">
+        <v>9400</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="1"/>
+        <v>-9400</v>
+      </c>
+      <c r="G61" s="4">
+        <f t="shared" si="2"/>
+        <v>-3208.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>95</v>
+      </c>
+      <c r="B62">
+        <f t="shared" si="3"/>
+        <v>207</v>
+      </c>
+      <c r="C62" s="5">
+        <f t="shared" si="4"/>
+        <v>606.4453125</v>
+      </c>
+      <c r="D62">
+        <v>9500</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="1"/>
+        <v>-9500</v>
+      </c>
+      <c r="G62" s="4">
+        <f t="shared" si="2"/>
+        <v>-3242.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>96</v>
+      </c>
+      <c r="B63" s="6">
+        <f t="shared" si="3"/>
+        <v>200</v>
+      </c>
+      <c r="C63" s="7">
+        <f t="shared" si="4"/>
+        <v>585.9375</v>
+      </c>
+      <c r="D63" s="6">
+        <v>9600</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="1"/>
+        <v>-9600</v>
+      </c>
+      <c r="G63" s="4">
+        <f t="shared" si="2"/>
+        <v>-3276.8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>97</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="3"/>
+        <v>194</v>
+      </c>
+      <c r="C64" s="5">
+        <f t="shared" si="4"/>
+        <v>568.359375</v>
+      </c>
+      <c r="D64">
+        <v>9700</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="1"/>
+        <v>-9700</v>
+      </c>
+      <c r="G64" s="4">
+        <f t="shared" si="2"/>
+        <v>-3310.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>98</v>
+      </c>
+      <c r="B65" s="6">
+        <f t="shared" si="3"/>
+        <v>188</v>
+      </c>
+      <c r="C65" s="7">
+        <f t="shared" si="4"/>
+        <v>550.78125</v>
+      </c>
+      <c r="D65" s="6">
+        <v>9800</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="1"/>
+        <v>-9800</v>
+      </c>
+      <c r="G65" s="4">
+        <f t="shared" si="2"/>
+        <v>-3345.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>99</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="3"/>
+        <v>181</v>
+      </c>
+      <c r="C66" s="5">
+        <f t="shared" si="4"/>
+        <v>530.2734375</v>
+      </c>
+      <c r="D66">
+        <v>9900</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="1"/>
+        <v>-9900</v>
+      </c>
+      <c r="G66" s="4">
+        <f t="shared" si="2"/>
+        <v>-3379.2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>100</v>
+      </c>
+      <c r="B67" s="6">
+        <f t="shared" si="3"/>
+        <v>175</v>
+      </c>
+      <c r="C67" s="7">
+        <f t="shared" si="4"/>
+        <v>512.6953125</v>
+      </c>
+      <c r="D67" s="6">
+        <v>10000</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6">
+        <f t="shared" si="1"/>
+        <v>-10000</v>
+      </c>
+      <c r="G67" s="9">
+        <f t="shared" si="2"/>
+        <v>-3413.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>101</v>
+      </c>
+      <c r="B68">
+        <f t="shared" si="3"/>
+        <v>169</v>
+      </c>
+      <c r="C68" s="5">
+        <f t="shared" si="4"/>
+        <v>495.1171875</v>
+      </c>
+      <c r="D68">
+        <v>10100</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="1"/>
+        <v>-10100</v>
+      </c>
+      <c r="G68" s="4">
+        <f t="shared" si="2"/>
+        <v>-3447.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>102</v>
+      </c>
+      <c r="B69" s="6">
+        <f t="shared" si="3"/>
+        <v>162</v>
+      </c>
+      <c r="C69" s="7">
+        <f t="shared" si="4"/>
+        <v>474.609375</v>
+      </c>
+      <c r="D69" s="6">
+        <v>10200</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="1"/>
+        <v>-10200</v>
+      </c>
+      <c r="G69" s="4">
+        <f t="shared" si="2"/>
+        <v>-3481.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>103</v>
+      </c>
+      <c r="B70">
+        <f t="shared" si="3"/>
+        <v>156</v>
+      </c>
+      <c r="C70" s="5">
+        <f t="shared" si="4"/>
+        <v>457.03125</v>
+      </c>
+      <c r="D70">
+        <v>10300</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="1"/>
+        <v>-10300</v>
+      </c>
+      <c r="G70" s="4">
+        <f t="shared" si="2"/>
+        <v>-3515.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>104</v>
+      </c>
+      <c r="B71" s="6">
+        <f t="shared" si="3"/>
+        <v>150</v>
+      </c>
+      <c r="C71" s="7">
+        <f t="shared" si="4"/>
+        <v>439.453125</v>
+      </c>
+      <c r="D71" s="6">
+        <v>10400</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="1"/>
+        <v>-10400</v>
+      </c>
+      <c r="G71" s="4">
+        <f t="shared" si="2"/>
+        <v>-3549.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>105</v>
+      </c>
+      <c r="B72">
+        <f t="shared" si="3"/>
+        <v>143</v>
+      </c>
+      <c r="C72" s="5">
+        <f t="shared" si="4"/>
+        <v>418.9453125</v>
+      </c>
+      <c r="D72">
+        <v>10500</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ref="F72:F82" si="5">E72-D72</f>
+        <v>-10500</v>
+      </c>
+      <c r="G72" s="4">
+        <f t="shared" ref="G72:G82" si="6">ROUND(F72/$I$2,1)</f>
+        <v>-3584</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>106</v>
+      </c>
+      <c r="B73" s="6">
+        <f t="shared" ref="B73:B87" si="7">ROUND($E$4-(((A73-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
+        <v>137</v>
+      </c>
+      <c r="C73" s="7">
+        <f t="shared" ref="C73:C87" si="8">B73*$E$1/$E$2</f>
+        <v>401.3671875</v>
+      </c>
+      <c r="D73" s="6">
+        <v>10600</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="5"/>
+        <v>-10600</v>
+      </c>
+      <c r="G73" s="4">
+        <f t="shared" si="6"/>
+        <v>-3618.1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>107</v>
+      </c>
+      <c r="B74">
+        <f t="shared" si="7"/>
+        <v>131</v>
+      </c>
+      <c r="C74" s="5">
+        <f t="shared" si="8"/>
+        <v>383.7890625</v>
+      </c>
+      <c r="D74">
+        <v>10700</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="5"/>
+        <v>-10700</v>
+      </c>
+      <c r="G74" s="4">
+        <f t="shared" si="6"/>
+        <v>-3652.3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>108</v>
+      </c>
+      <c r="B75" s="6">
+        <f t="shared" si="7"/>
+        <v>124</v>
+      </c>
+      <c r="C75" s="7">
+        <f t="shared" si="8"/>
+        <v>363.28125</v>
+      </c>
+      <c r="D75" s="6">
+        <v>10800</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="5"/>
+        <v>-10800</v>
+      </c>
+      <c r="G75" s="4">
+        <f t="shared" si="6"/>
+        <v>-3686.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>109</v>
+      </c>
+      <c r="B76">
+        <f t="shared" si="7"/>
+        <v>118</v>
+      </c>
+      <c r="C76" s="5">
+        <f t="shared" si="8"/>
+        <v>345.703125</v>
+      </c>
+      <c r="D76">
+        <v>10900</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="5"/>
+        <v>-10900</v>
+      </c>
+      <c r="G76" s="4">
+        <f t="shared" si="6"/>
+        <v>-3720.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>110</v>
+      </c>
+      <c r="B77" s="6">
+        <f t="shared" si="7"/>
+        <v>111</v>
+      </c>
+      <c r="C77" s="7">
+        <f t="shared" si="8"/>
+        <v>325.1953125</v>
+      </c>
+      <c r="D77" s="6">
+        <v>11000</v>
+      </c>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6">
+        <f t="shared" si="5"/>
+        <v>-11000</v>
+      </c>
+      <c r="G77" s="9">
+        <f t="shared" si="6"/>
+        <v>-3754.7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>111</v>
+      </c>
+      <c r="B78">
+        <f t="shared" si="7"/>
+        <v>105</v>
+      </c>
+      <c r="C78" s="5">
+        <f t="shared" si="8"/>
+        <v>307.6171875</v>
+      </c>
+      <c r="D78">
+        <v>11100</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="5"/>
+        <v>-11100</v>
+      </c>
+      <c r="G78" s="4">
+        <f t="shared" si="6"/>
+        <v>-3788.8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>112</v>
+      </c>
+      <c r="B79" s="6">
+        <f t="shared" si="7"/>
+        <v>99</v>
+      </c>
+      <c r="C79" s="7">
+        <f t="shared" si="8"/>
+        <v>290.0390625</v>
+      </c>
+      <c r="D79" s="6">
+        <v>11200</v>
+      </c>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6">
+        <f t="shared" si="5"/>
+        <v>-11200</v>
+      </c>
+      <c r="G79" s="9">
+        <f t="shared" si="6"/>
+        <v>-3822.9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>113</v>
+      </c>
+      <c r="B80">
+        <f t="shared" si="7"/>
+        <v>92</v>
+      </c>
+      <c r="C80" s="5">
+        <f t="shared" si="8"/>
+        <v>269.53125</v>
+      </c>
+      <c r="D80">
+        <v>11300</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="5"/>
+        <v>-11300</v>
+      </c>
+      <c r="G80" s="4">
+        <f t="shared" si="6"/>
+        <v>-3857.1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>114</v>
+      </c>
+      <c r="B81" s="6">
+        <f t="shared" si="7"/>
+        <v>86</v>
+      </c>
+      <c r="C81" s="7">
+        <f t="shared" si="8"/>
+        <v>251.953125</v>
+      </c>
+      <c r="D81" s="6">
+        <v>11400</v>
+      </c>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6">
+        <f t="shared" si="5"/>
+        <v>-11400</v>
+      </c>
+      <c r="G81" s="9">
+        <f t="shared" si="6"/>
+        <v>-3891.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>115</v>
+      </c>
+      <c r="B82">
+        <f t="shared" si="7"/>
+        <v>80</v>
+      </c>
+      <c r="C82" s="5">
+        <f t="shared" si="8"/>
+        <v>234.375</v>
+      </c>
+      <c r="D82">
+        <v>11500</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="5"/>
+        <v>-11500</v>
+      </c>
+      <c r="G82" s="4">
+        <f t="shared" si="6"/>
+        <v>-3925.3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>116</v>
+      </c>
+      <c r="B83" s="6">
+        <f t="shared" si="7"/>
+        <v>73</v>
+      </c>
+      <c r="C83" s="7">
+        <f t="shared" si="8"/>
+        <v>213.8671875</v>
+      </c>
+      <c r="D83" s="6">
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>117</v>
+      </c>
+      <c r="B84">
+        <f t="shared" si="7"/>
+        <v>67</v>
+      </c>
+      <c r="C84" s="5">
+        <f t="shared" si="8"/>
+        <v>196.2890625</v>
+      </c>
+      <c r="D84">
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>118</v>
+      </c>
+      <c r="B85" s="6">
+        <f t="shared" si="7"/>
+        <v>61</v>
+      </c>
+      <c r="C85" s="7">
+        <f t="shared" si="8"/>
+        <v>178.7109375</v>
+      </c>
+      <c r="D85" s="6">
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>119</v>
+      </c>
+      <c r="B86">
+        <f t="shared" si="7"/>
+        <v>54</v>
+      </c>
+      <c r="C86" s="5">
+        <f t="shared" si="8"/>
+        <v>158.203125</v>
+      </c>
+      <c r="D86">
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>120</v>
+      </c>
+      <c r="B87" s="6">
+        <f t="shared" si="7"/>
+        <v>48</v>
+      </c>
+      <c r="C87" s="7">
+        <f t="shared" si="8"/>
+        <v>140.625</v>
+      </c>
+      <c r="D87" s="6">
+        <v>12000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/01.Documentation/01.Diseño/Calibracion DAC.xlsx
+++ b/01.Documentation/01.Diseño/Calibracion DAC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\javie\Team Dropbox\JRODRIGUEZ\Repositorios\01.Rover\01.Documentation\01.Diseño\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A29F89DD-081B-4415-B3A2-22DAFD77D9DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1444FCAA-1ABC-4E28-8E02-99A19B12C303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-25290" yWindow="3510" windowWidth="21600" windowHeight="11295" firstSheet="4" activeTab="4" xr2:uid="{1F2CF652-4A2E-4701-B4BE-D2C83886312B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{1F2CF652-4A2E-4701-B4BE-D2C83886312B}"/>
   </bookViews>
   <sheets>
     <sheet name="120-1420" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,9 @@
     <sheet name="Tarjeta verificacion" sheetId="3" r:id="rId3"/>
     <sheet name="140-1435 (2)" sheetId="4" r:id="rId4"/>
     <sheet name="140-1435 (3)" sheetId="5" r:id="rId5"/>
+    <sheet name="40-180" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="20">
   <si>
     <t>DAC count</t>
   </si>
@@ -112,7 +113,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,8 +128,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,6 +155,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -160,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -175,6 +189,8 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4149,6 +4165,1961 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000000-A8B3-4397-96EA-E925A432147C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1955612608"/>
+        <c:axId val="1955616352"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1955612608"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1955616352"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1955616352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1955612608"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'40-180'!$D$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vout teorico
+(mV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'40-180'!$D$7:$D$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5200</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5400</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5600</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6200</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6400</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6600</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7400</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7600</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8200</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8400</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8600</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9200</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9400</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9600</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9800</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9900</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>10100</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>10300</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>10400</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>10500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>10600</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>10700</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10800</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-D2F1-4EEA-A071-4889D21330BC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'40-180'!$E$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Vout medido
+(mV) </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:val>
+            <c:numRef>
+              <c:f>'40-180'!$E$7:$E$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D2F1-4EEA-A071-4889D21330BC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1693085360"/>
+        <c:axId val="1693088272"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1693085360"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1693088272"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1693088272"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="13000"/>
+          <c:min val="4000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1693085360"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'40-180'!$F$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Error(mV)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'40-180'!$D$7:$D$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5200</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5400</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5600</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6200</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6400</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6600</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7400</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7600</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8200</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8400</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8600</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9200</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9400</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9600</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9800</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9900</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>10100</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>10300</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>10400</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>10500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>10600</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>10700</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10800</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'40-180'!$F$7:$F$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>-4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-4200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-4400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-4500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-4600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-4700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-4800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-4900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-5100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-5200</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-5300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-5400</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-5500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-5600</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-5700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-5800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-5900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-6000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-6100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-6200</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-6300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-6400</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-6500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-6600</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-6700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-6800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-6900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-7000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-7100</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-7200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-7300</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-7400</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-7500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-7600</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-7700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-7800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-8000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-8100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-8200</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-8300</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-8400</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-8500</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-8600</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-8700</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-8800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-8900</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-9000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-9100</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-9200</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-9300</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-9400</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-9500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-9600</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-9700</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-9800</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-9900</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-10000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-10100</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-10200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-10300</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-10400</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-10500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-10600</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-10700</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-10800</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-10900</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2254-4B02-A39F-4C572046580B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="1959899648"/>
+        <c:axId val="1959900064"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="1959899648"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="12000"/>
+          <c:min val="5000"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1959900064"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1959900064"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-ES"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1959899648"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-ES"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-ES"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'40-180'!$G$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Err(q)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'40-180'!$D$7:$D$77</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>4000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>4200</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4300</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4500</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>4600</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>4700</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4800</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>4900</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>5100</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>5200</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>5300</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>5400</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>5500</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>5600</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>5700</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>5800</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>5900</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6100</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6200</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6300</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6400</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6500</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6600</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>6700</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>6800</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6900</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7100</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7200</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>7300</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7400</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7500</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7600</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7700</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7800</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>7900</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8100</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8200</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8300</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>8400</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>8500</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>8600</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>8700</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>8800</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>8900</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>9000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>9100</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>9200</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>9300</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>9400</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>9500</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>9600</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9700</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>9800</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>9900</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>10000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>10100</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>10200</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>10300</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>10400</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>10500</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>10600</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>10700</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10800</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>10900</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>11000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'40-180'!$G$7:$G$77</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="71"/>
+                <c:pt idx="0">
+                  <c:v>-1365.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1399.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-1433.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-1467.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-1501.9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-1536</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-1570.1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-1604.3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-1638.4</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-1672.5</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-1706.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-1740.8</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-1774.9</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-1809.1</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-1843.2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-1877.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1911.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1945.6</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1979.7</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-2013.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-2048</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-2082.1</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-2116.3000000000002</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-2150.4</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-2184.5</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-2218.6999999999998</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-2252.8000000000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-2286.9</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-2321.1</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-2355.1999999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-2389.3000000000002</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-2423.5</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-2457.6</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-2491.6999999999998</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-2525.9</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-2560</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-2594.1</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-2628.3</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-2662.4</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-2696.5</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-2730.7</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-2764.8</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-2798.9</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-2833.1</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-2867.2</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>-2901.3</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>-2935.5</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>-2969.6</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>-3003.7</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>-3037.9</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>-3072</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>-3106.1</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>-3140.3</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>-3174.4</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>-3208.5</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>-3242.7</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>-3276.8</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>-3310.9</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>-3345.1</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>-3379.2</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>-3413.3</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>-3447.5</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>-3481.6</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>-3515.7</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>-3549.9</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>-3584</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>-3618.1</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>-3652.3</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>-3686.4</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>-3720.5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>-3754.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A7C5-41A8-9BE0-C146EF8D8DFC}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10153,6 +12124,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -13041,6 +15132,1541 @@
 </file>
 
 <file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -18194,6 +21820,125 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>71437</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B953A79-1F6C-4CFB-8932-A852353EC879}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>4762</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2524284C-3965-4DD9-8CAB-2F78ECA4543E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>33337</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4C4035FD-19DC-445C-8E1E-967CA4A2079D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
@@ -26397,7 +30142,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="6">
-        <f t="shared" ref="B7:B70" si="0">ROUND($E$4-(((A7-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
+        <f t="shared" ref="B7:B8" si="0">ROUND($E$4-(((A7-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
         <v>556</v>
       </c>
       <c r="C7" s="7">
@@ -28304,6 +32049,3231 @@
       </c>
       <c r="D87" s="6">
         <v>12000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F292A6FE-113C-4C36-9E10-B4EB846C4EAB}">
+  <dimension ref="A1:J152"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1">
+        <v>185</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1">
+        <v>3000</v>
+      </c>
+      <c r="F1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2">
+        <v>40</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1024</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3">
+        <f>E1/E2</f>
+        <v>2.9296875</v>
+      </c>
+      <c r="J2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>270</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <f>ROUND(B3*E2/E1,0)</f>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>2540</v>
+      </c>
+      <c r="C4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>ROUND( B4*E2/E1,0)</f>
+        <v>867</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="6" spans="1:10" s="1" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
+        <v>40</v>
+      </c>
+      <c r="B7" s="10">
+        <f t="shared" ref="B7:B70" si="0">ROUND($E$4-(((A7-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
+        <v>867</v>
+      </c>
+      <c r="C7" s="11">
+        <f>B7*$E$1/$E$2</f>
+        <v>2540.0390625</v>
+      </c>
+      <c r="D7" s="10">
+        <f>A7*100</f>
+        <v>4000</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6">
+        <f>E7-D7</f>
+        <v>-4000</v>
+      </c>
+      <c r="G7" s="9">
+        <f>ROUND(F7/$I$2,1)</f>
+        <v>-1365.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
+        <v>41</v>
+      </c>
+      <c r="B8" s="10">
+        <f t="shared" si="0"/>
+        <v>862</v>
+      </c>
+      <c r="C8" s="11">
+        <f>B8*$E$1/$E$2</f>
+        <v>2525.390625</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" ref="D8:D71" si="1">A8*100</f>
+        <v>4100</v>
+      </c>
+      <c r="F8">
+        <f t="shared" ref="F8:F71" si="2">E8-D8</f>
+        <v>-4100</v>
+      </c>
+      <c r="G8" s="4">
+        <f t="shared" ref="G8:G71" si="3">ROUND(F8/$I$2,1)</f>
+        <v>-1399.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
+        <v>42</v>
+      </c>
+      <c r="B9" s="10">
+        <f t="shared" si="0"/>
+        <v>856</v>
+      </c>
+      <c r="C9" s="11">
+        <f t="shared" ref="C9:C72" si="4">B9*$E$1/$E$2</f>
+        <v>2507.8125</v>
+      </c>
+      <c r="D9" s="10">
+        <f t="shared" si="1"/>
+        <v>4200</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>-4200</v>
+      </c>
+      <c r="G9" s="4">
+        <f t="shared" si="3"/>
+        <v>-1433.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
+        <v>43</v>
+      </c>
+      <c r="B10" s="10">
+        <f t="shared" si="0"/>
+        <v>851</v>
+      </c>
+      <c r="C10" s="11">
+        <f t="shared" si="4"/>
+        <v>2493.1640625</v>
+      </c>
+      <c r="D10" s="10">
+        <f t="shared" si="1"/>
+        <v>4300</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>-4300</v>
+      </c>
+      <c r="G10" s="4">
+        <f t="shared" si="3"/>
+        <v>-1467.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
+        <v>44</v>
+      </c>
+      <c r="B11" s="10">
+        <f t="shared" si="0"/>
+        <v>846</v>
+      </c>
+      <c r="C11" s="11">
+        <f t="shared" si="4"/>
+        <v>2478.515625</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" si="1"/>
+        <v>4400</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="2"/>
+        <v>-4400</v>
+      </c>
+      <c r="G11" s="4">
+        <f t="shared" si="3"/>
+        <v>-1501.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>45</v>
+      </c>
+      <c r="B12" s="10">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="C12" s="11">
+        <f t="shared" si="4"/>
+        <v>2460.9375</v>
+      </c>
+      <c r="D12" s="10">
+        <f t="shared" si="1"/>
+        <v>4500</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>-4500</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="3"/>
+        <v>-1536</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
+        <v>46</v>
+      </c>
+      <c r="B13" s="10">
+        <f t="shared" si="0"/>
+        <v>835</v>
+      </c>
+      <c r="C13" s="11">
+        <f t="shared" si="4"/>
+        <v>2446.2890625</v>
+      </c>
+      <c r="D13" s="10">
+        <f t="shared" si="1"/>
+        <v>4600</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="2"/>
+        <v>-4600</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="3"/>
+        <v>-1570.1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
+        <v>47</v>
+      </c>
+      <c r="B14" s="10">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="C14" s="11">
+        <f t="shared" si="4"/>
+        <v>2431.640625</v>
+      </c>
+      <c r="D14" s="10">
+        <f t="shared" si="1"/>
+        <v>4700</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="2"/>
+        <v>-4700</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="3"/>
+        <v>-1604.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>48</v>
+      </c>
+      <c r="B15" s="10">
+        <f t="shared" si="0"/>
+        <v>824</v>
+      </c>
+      <c r="C15" s="11">
+        <f t="shared" si="4"/>
+        <v>2414.0625</v>
+      </c>
+      <c r="D15" s="10">
+        <f t="shared" si="1"/>
+        <v>4800</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>-4800</v>
+      </c>
+      <c r="G15" s="4">
+        <f t="shared" si="3"/>
+        <v>-1638.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>49</v>
+      </c>
+      <c r="B16" s="10">
+        <f t="shared" si="0"/>
+        <v>819</v>
+      </c>
+      <c r="C16" s="11">
+        <f t="shared" si="4"/>
+        <v>2399.4140625</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" si="1"/>
+        <v>4900</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="2"/>
+        <v>-4900</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="3"/>
+        <v>-1672.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
+        <v>50</v>
+      </c>
+      <c r="B17" s="10">
+        <f t="shared" si="0"/>
+        <v>814</v>
+      </c>
+      <c r="C17" s="11">
+        <f t="shared" si="4"/>
+        <v>2384.765625</v>
+      </c>
+      <c r="D17" s="10">
+        <f t="shared" si="1"/>
+        <v>5000</v>
+      </c>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6">
+        <f t="shared" si="2"/>
+        <v>-5000</v>
+      </c>
+      <c r="G17" s="9">
+        <f t="shared" si="3"/>
+        <v>-1706.7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
+        <v>51</v>
+      </c>
+      <c r="B18" s="10">
+        <f t="shared" si="0"/>
+        <v>808</v>
+      </c>
+      <c r="C18" s="11">
+        <f t="shared" si="4"/>
+        <v>2367.1875</v>
+      </c>
+      <c r="D18" s="10">
+        <f t="shared" si="1"/>
+        <v>5100</v>
+      </c>
+      <c r="F18">
+        <f t="shared" si="2"/>
+        <v>-5100</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="3"/>
+        <v>-1740.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>52</v>
+      </c>
+      <c r="B19" s="10">
+        <f t="shared" si="0"/>
+        <v>803</v>
+      </c>
+      <c r="C19" s="11">
+        <f t="shared" si="4"/>
+        <v>2352.5390625</v>
+      </c>
+      <c r="D19" s="10">
+        <f t="shared" si="1"/>
+        <v>5200</v>
+      </c>
+      <c r="F19">
+        <f t="shared" si="2"/>
+        <v>-5200</v>
+      </c>
+      <c r="G19" s="4">
+        <f t="shared" si="3"/>
+        <v>-1774.9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>53</v>
+      </c>
+      <c r="B20" s="10">
+        <f t="shared" si="0"/>
+        <v>798</v>
+      </c>
+      <c r="C20" s="11">
+        <f t="shared" si="4"/>
+        <v>2337.890625</v>
+      </c>
+      <c r="D20" s="10">
+        <f t="shared" si="1"/>
+        <v>5300</v>
+      </c>
+      <c r="F20">
+        <f t="shared" si="2"/>
+        <v>-5300</v>
+      </c>
+      <c r="G20" s="4">
+        <f t="shared" si="3"/>
+        <v>-1809.1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>54</v>
+      </c>
+      <c r="B21" s="10">
+        <f t="shared" si="0"/>
+        <v>792</v>
+      </c>
+      <c r="C21" s="11">
+        <f t="shared" si="4"/>
+        <v>2320.3125</v>
+      </c>
+      <c r="D21" s="10">
+        <f t="shared" si="1"/>
+        <v>5400</v>
+      </c>
+      <c r="F21">
+        <f t="shared" si="2"/>
+        <v>-5400</v>
+      </c>
+      <c r="G21" s="4">
+        <f t="shared" si="3"/>
+        <v>-1843.2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="6">
+        <v>55</v>
+      </c>
+      <c r="B22" s="10">
+        <f t="shared" si="0"/>
+        <v>787</v>
+      </c>
+      <c r="C22" s="11">
+        <f t="shared" si="4"/>
+        <v>2305.6640625</v>
+      </c>
+      <c r="D22" s="10">
+        <f t="shared" si="1"/>
+        <v>5500</v>
+      </c>
+      <c r="F22">
+        <f t="shared" si="2"/>
+        <v>-5500</v>
+      </c>
+      <c r="G22" s="4">
+        <f t="shared" si="3"/>
+        <v>-1877.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="6">
+        <v>56</v>
+      </c>
+      <c r="B23" s="10">
+        <f t="shared" si="0"/>
+        <v>781</v>
+      </c>
+      <c r="C23" s="11">
+        <f t="shared" si="4"/>
+        <v>2288.0859375</v>
+      </c>
+      <c r="D23" s="10">
+        <f t="shared" si="1"/>
+        <v>5600</v>
+      </c>
+      <c r="F23">
+        <f t="shared" si="2"/>
+        <v>-5600</v>
+      </c>
+      <c r="G23" s="4">
+        <f t="shared" si="3"/>
+        <v>-1911.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="6">
+        <v>57</v>
+      </c>
+      <c r="B24" s="10">
+        <f t="shared" si="0"/>
+        <v>776</v>
+      </c>
+      <c r="C24" s="11">
+        <f t="shared" si="4"/>
+        <v>2273.4375</v>
+      </c>
+      <c r="D24" s="10">
+        <f t="shared" si="1"/>
+        <v>5700</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="2"/>
+        <v>-5700</v>
+      </c>
+      <c r="G24" s="4">
+        <f t="shared" si="3"/>
+        <v>-1945.6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="6">
+        <v>58</v>
+      </c>
+      <c r="B25" s="10">
+        <f t="shared" si="0"/>
+        <v>771</v>
+      </c>
+      <c r="C25" s="11">
+        <f t="shared" si="4"/>
+        <v>2258.7890625</v>
+      </c>
+      <c r="D25" s="10">
+        <f t="shared" si="1"/>
+        <v>5800</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="2"/>
+        <v>-5800</v>
+      </c>
+      <c r="G25" s="4">
+        <f t="shared" si="3"/>
+        <v>-1979.7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="6">
+        <v>59</v>
+      </c>
+      <c r="B26" s="10">
+        <f t="shared" si="0"/>
+        <v>765</v>
+      </c>
+      <c r="C26" s="11">
+        <f t="shared" si="4"/>
+        <v>2241.2109375</v>
+      </c>
+      <c r="D26" s="10">
+        <f t="shared" si="1"/>
+        <v>5900</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="2"/>
+        <v>-5900</v>
+      </c>
+      <c r="G26" s="4">
+        <f t="shared" si="3"/>
+        <v>-2013.9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="6">
+        <v>60</v>
+      </c>
+      <c r="B27" s="10">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="C27" s="11">
+        <f t="shared" si="4"/>
+        <v>2226.5625</v>
+      </c>
+      <c r="D27" s="10">
+        <f t="shared" si="1"/>
+        <v>6000</v>
+      </c>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6">
+        <f t="shared" si="2"/>
+        <v>-6000</v>
+      </c>
+      <c r="G27" s="9">
+        <f t="shared" si="3"/>
+        <v>-2048</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>61</v>
+      </c>
+      <c r="B28" s="10">
+        <f t="shared" si="0"/>
+        <v>755</v>
+      </c>
+      <c r="C28" s="11">
+        <f t="shared" si="4"/>
+        <v>2211.9140625</v>
+      </c>
+      <c r="D28" s="10">
+        <f t="shared" si="1"/>
+        <v>6100</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="2"/>
+        <v>-6100</v>
+      </c>
+      <c r="G28" s="4">
+        <f t="shared" si="3"/>
+        <v>-2082.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="6">
+        <v>62</v>
+      </c>
+      <c r="B29" s="10">
+        <f t="shared" si="0"/>
+        <v>749</v>
+      </c>
+      <c r="C29" s="11">
+        <f t="shared" si="4"/>
+        <v>2194.3359375</v>
+      </c>
+      <c r="D29" s="10">
+        <f t="shared" si="1"/>
+        <v>6200</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="2"/>
+        <v>-6200</v>
+      </c>
+      <c r="G29" s="4">
+        <f t="shared" si="3"/>
+        <v>-2116.3000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="6">
+        <v>63</v>
+      </c>
+      <c r="B30" s="10">
+        <f t="shared" si="0"/>
+        <v>744</v>
+      </c>
+      <c r="C30" s="11">
+        <f t="shared" si="4"/>
+        <v>2179.6875</v>
+      </c>
+      <c r="D30" s="10">
+        <f t="shared" si="1"/>
+        <v>6300</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="2"/>
+        <v>-6300</v>
+      </c>
+      <c r="G30" s="4">
+        <f t="shared" si="3"/>
+        <v>-2150.4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>64</v>
+      </c>
+      <c r="B31" s="10">
+        <f t="shared" si="0"/>
+        <v>739</v>
+      </c>
+      <c r="C31" s="11">
+        <f t="shared" si="4"/>
+        <v>2165.0390625</v>
+      </c>
+      <c r="D31" s="10">
+        <f t="shared" si="1"/>
+        <v>6400</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="2"/>
+        <v>-6400</v>
+      </c>
+      <c r="G31" s="4">
+        <f t="shared" si="3"/>
+        <v>-2184.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="6">
+        <v>65</v>
+      </c>
+      <c r="B32" s="10">
+        <f t="shared" si="0"/>
+        <v>733</v>
+      </c>
+      <c r="C32" s="11">
+        <f t="shared" si="4"/>
+        <v>2147.4609375</v>
+      </c>
+      <c r="D32" s="10">
+        <f t="shared" si="1"/>
+        <v>6500</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="2"/>
+        <v>-6500</v>
+      </c>
+      <c r="G32" s="4">
+        <f t="shared" si="3"/>
+        <v>-2218.6999999999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="6">
+        <v>66</v>
+      </c>
+      <c r="B33" s="10">
+        <f t="shared" si="0"/>
+        <v>728</v>
+      </c>
+      <c r="C33" s="11">
+        <f t="shared" si="4"/>
+        <v>2132.8125</v>
+      </c>
+      <c r="D33" s="10">
+        <f t="shared" si="1"/>
+        <v>6600</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="2"/>
+        <v>-6600</v>
+      </c>
+      <c r="G33" s="4">
+        <f t="shared" si="3"/>
+        <v>-2252.8000000000002</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="6">
+        <v>67</v>
+      </c>
+      <c r="B34" s="10">
+        <f t="shared" si="0"/>
+        <v>723</v>
+      </c>
+      <c r="C34" s="11">
+        <f t="shared" si="4"/>
+        <v>2118.1640625</v>
+      </c>
+      <c r="D34" s="10">
+        <f t="shared" si="1"/>
+        <v>6700</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="2"/>
+        <v>-6700</v>
+      </c>
+      <c r="G34" s="4">
+        <f t="shared" si="3"/>
+        <v>-2286.9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="6">
+        <v>68</v>
+      </c>
+      <c r="B35" s="10">
+        <f t="shared" si="0"/>
+        <v>717</v>
+      </c>
+      <c r="C35" s="11">
+        <f t="shared" si="4"/>
+        <v>2100.5859375</v>
+      </c>
+      <c r="D35" s="10">
+        <f t="shared" si="1"/>
+        <v>6800</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="2"/>
+        <v>-6800</v>
+      </c>
+      <c r="G35" s="4">
+        <f t="shared" si="3"/>
+        <v>-2321.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="6">
+        <v>69</v>
+      </c>
+      <c r="B36" s="10">
+        <f t="shared" si="0"/>
+        <v>712</v>
+      </c>
+      <c r="C36" s="11">
+        <f t="shared" si="4"/>
+        <v>2085.9375</v>
+      </c>
+      <c r="D36" s="10">
+        <f t="shared" si="1"/>
+        <v>6900</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="2"/>
+        <v>-6900</v>
+      </c>
+      <c r="G36" s="4">
+        <f t="shared" si="3"/>
+        <v>-2355.1999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>70</v>
+      </c>
+      <c r="B37" s="10">
+        <f t="shared" si="0"/>
+        <v>707</v>
+      </c>
+      <c r="C37" s="11">
+        <f t="shared" si="4"/>
+        <v>2071.2890625</v>
+      </c>
+      <c r="D37" s="10">
+        <f t="shared" si="1"/>
+        <v>7000</v>
+      </c>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6">
+        <f t="shared" si="2"/>
+        <v>-7000</v>
+      </c>
+      <c r="G37" s="9">
+        <f t="shared" si="3"/>
+        <v>-2389.3000000000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="6">
+        <v>71</v>
+      </c>
+      <c r="B38" s="10">
+        <f t="shared" si="0"/>
+        <v>701</v>
+      </c>
+      <c r="C38" s="11">
+        <f t="shared" si="4"/>
+        <v>2053.7109375</v>
+      </c>
+      <c r="D38" s="10">
+        <f t="shared" si="1"/>
+        <v>7100</v>
+      </c>
+      <c r="F38">
+        <f t="shared" si="2"/>
+        <v>-7100</v>
+      </c>
+      <c r="G38" s="4">
+        <f t="shared" si="3"/>
+        <v>-2423.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="6">
+        <v>72</v>
+      </c>
+      <c r="B39" s="10">
+        <f t="shared" si="0"/>
+        <v>696</v>
+      </c>
+      <c r="C39" s="11">
+        <f t="shared" si="4"/>
+        <v>2039.0625</v>
+      </c>
+      <c r="D39" s="10">
+        <f t="shared" si="1"/>
+        <v>7200</v>
+      </c>
+      <c r="F39">
+        <f t="shared" si="2"/>
+        <v>-7200</v>
+      </c>
+      <c r="G39" s="4">
+        <f t="shared" si="3"/>
+        <v>-2457.6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="6">
+        <v>73</v>
+      </c>
+      <c r="B40" s="10">
+        <f t="shared" si="0"/>
+        <v>691</v>
+      </c>
+      <c r="C40" s="11">
+        <f t="shared" si="4"/>
+        <v>2024.4140625</v>
+      </c>
+      <c r="D40" s="10">
+        <f t="shared" si="1"/>
+        <v>7300</v>
+      </c>
+      <c r="F40">
+        <f t="shared" si="2"/>
+        <v>-7300</v>
+      </c>
+      <c r="G40" s="4">
+        <f t="shared" si="3"/>
+        <v>-2491.6999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="6">
+        <v>74</v>
+      </c>
+      <c r="B41" s="10">
+        <f t="shared" si="0"/>
+        <v>685</v>
+      </c>
+      <c r="C41" s="11">
+        <f t="shared" si="4"/>
+        <v>2006.8359375</v>
+      </c>
+      <c r="D41" s="10">
+        <f t="shared" si="1"/>
+        <v>7400</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="2"/>
+        <v>-7400</v>
+      </c>
+      <c r="G41" s="4">
+        <f t="shared" si="3"/>
+        <v>-2525.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>75</v>
+      </c>
+      <c r="B42" s="10">
+        <f t="shared" si="0"/>
+        <v>680</v>
+      </c>
+      <c r="C42" s="11">
+        <f t="shared" si="4"/>
+        <v>1992.1875</v>
+      </c>
+      <c r="D42" s="10">
+        <f t="shared" si="1"/>
+        <v>7500</v>
+      </c>
+      <c r="F42">
+        <f t="shared" si="2"/>
+        <v>-7500</v>
+      </c>
+      <c r="G42" s="4">
+        <f t="shared" si="3"/>
+        <v>-2560</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="6">
+        <v>76</v>
+      </c>
+      <c r="B43" s="10">
+        <f t="shared" si="0"/>
+        <v>675</v>
+      </c>
+      <c r="C43" s="11">
+        <f t="shared" si="4"/>
+        <v>1977.5390625</v>
+      </c>
+      <c r="D43" s="10">
+        <f t="shared" si="1"/>
+        <v>7600</v>
+      </c>
+      <c r="F43">
+        <f t="shared" si="2"/>
+        <v>-7600</v>
+      </c>
+      <c r="G43" s="4">
+        <f t="shared" si="3"/>
+        <v>-2594.1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="6">
+        <v>77</v>
+      </c>
+      <c r="B44" s="10">
+        <f t="shared" si="0"/>
+        <v>669</v>
+      </c>
+      <c r="C44" s="11">
+        <f t="shared" si="4"/>
+        <v>1959.9609375</v>
+      </c>
+      <c r="D44" s="10">
+        <f t="shared" si="1"/>
+        <v>7700</v>
+      </c>
+      <c r="F44">
+        <f t="shared" si="2"/>
+        <v>-7700</v>
+      </c>
+      <c r="G44" s="4">
+        <f t="shared" si="3"/>
+        <v>-2628.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="6">
+        <v>78</v>
+      </c>
+      <c r="B45" s="10">
+        <f t="shared" si="0"/>
+        <v>664</v>
+      </c>
+      <c r="C45" s="11">
+        <f t="shared" si="4"/>
+        <v>1945.3125</v>
+      </c>
+      <c r="D45" s="10">
+        <f t="shared" si="1"/>
+        <v>7800</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="2"/>
+        <v>-7800</v>
+      </c>
+      <c r="G45" s="4">
+        <f t="shared" si="3"/>
+        <v>-2662.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="6">
+        <v>79</v>
+      </c>
+      <c r="B46" s="10">
+        <f t="shared" si="0"/>
+        <v>659</v>
+      </c>
+      <c r="C46" s="11">
+        <f t="shared" si="4"/>
+        <v>1930.6640625</v>
+      </c>
+      <c r="D46" s="10">
+        <f t="shared" si="1"/>
+        <v>7900</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="2"/>
+        <v>-7900</v>
+      </c>
+      <c r="G46" s="4">
+        <f t="shared" si="3"/>
+        <v>-2696.5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>80</v>
+      </c>
+      <c r="B47" s="10">
+        <f t="shared" si="0"/>
+        <v>653</v>
+      </c>
+      <c r="C47" s="11">
+        <f t="shared" si="4"/>
+        <v>1913.0859375</v>
+      </c>
+      <c r="D47" s="10">
+        <f t="shared" si="1"/>
+        <v>8000</v>
+      </c>
+      <c r="E47" s="6"/>
+      <c r="F47" s="6">
+        <f t="shared" si="2"/>
+        <v>-8000</v>
+      </c>
+      <c r="G47" s="9">
+        <f t="shared" si="3"/>
+        <v>-2730.7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="6">
+        <v>81</v>
+      </c>
+      <c r="B48" s="10">
+        <f t="shared" si="0"/>
+        <v>648</v>
+      </c>
+      <c r="C48" s="11">
+        <f t="shared" si="4"/>
+        <v>1898.4375</v>
+      </c>
+      <c r="D48" s="10">
+        <f t="shared" si="1"/>
+        <v>8100</v>
+      </c>
+      <c r="F48">
+        <f t="shared" si="2"/>
+        <v>-8100</v>
+      </c>
+      <c r="G48" s="4">
+        <f t="shared" si="3"/>
+        <v>-2764.8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="6">
+        <v>82</v>
+      </c>
+      <c r="B49" s="10">
+        <f t="shared" si="0"/>
+        <v>643</v>
+      </c>
+      <c r="C49" s="11">
+        <f t="shared" si="4"/>
+        <v>1883.7890625</v>
+      </c>
+      <c r="D49" s="10">
+        <f t="shared" si="1"/>
+        <v>8200</v>
+      </c>
+      <c r="F49">
+        <f t="shared" si="2"/>
+        <v>-8200</v>
+      </c>
+      <c r="G49" s="4">
+        <f t="shared" si="3"/>
+        <v>-2798.9</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="6">
+        <v>83</v>
+      </c>
+      <c r="B50" s="10">
+        <f t="shared" si="0"/>
+        <v>637</v>
+      </c>
+      <c r="C50" s="11">
+        <f t="shared" si="4"/>
+        <v>1866.2109375</v>
+      </c>
+      <c r="D50" s="10">
+        <f t="shared" si="1"/>
+        <v>8300</v>
+      </c>
+      <c r="F50">
+        <f t="shared" si="2"/>
+        <v>-8300</v>
+      </c>
+      <c r="G50" s="4">
+        <f t="shared" si="3"/>
+        <v>-2833.1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="6">
+        <v>84</v>
+      </c>
+      <c r="B51" s="10">
+        <f t="shared" si="0"/>
+        <v>632</v>
+      </c>
+      <c r="C51" s="11">
+        <f t="shared" si="4"/>
+        <v>1851.5625</v>
+      </c>
+      <c r="D51" s="10">
+        <f t="shared" si="1"/>
+        <v>8400</v>
+      </c>
+      <c r="F51">
+        <f t="shared" si="2"/>
+        <v>-8400</v>
+      </c>
+      <c r="G51" s="4">
+        <f t="shared" si="3"/>
+        <v>-2867.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="6">
+        <v>85</v>
+      </c>
+      <c r="B52" s="10">
+        <f t="shared" si="0"/>
+        <v>626</v>
+      </c>
+      <c r="C52" s="11">
+        <f t="shared" si="4"/>
+        <v>1833.984375</v>
+      </c>
+      <c r="D52" s="10">
+        <f t="shared" si="1"/>
+        <v>8500</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="2"/>
+        <v>-8500</v>
+      </c>
+      <c r="G52" s="4">
+        <f t="shared" si="3"/>
+        <v>-2901.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="6">
+        <v>86</v>
+      </c>
+      <c r="B53" s="10">
+        <f t="shared" si="0"/>
+        <v>621</v>
+      </c>
+      <c r="C53" s="11">
+        <f t="shared" si="4"/>
+        <v>1819.3359375</v>
+      </c>
+      <c r="D53" s="10">
+        <f t="shared" si="1"/>
+        <v>8600</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="2"/>
+        <v>-8600</v>
+      </c>
+      <c r="G53" s="4">
+        <f t="shared" si="3"/>
+        <v>-2935.5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>87</v>
+      </c>
+      <c r="B54" s="10">
+        <f t="shared" si="0"/>
+        <v>616</v>
+      </c>
+      <c r="C54" s="11">
+        <f t="shared" si="4"/>
+        <v>1804.6875</v>
+      </c>
+      <c r="D54" s="10">
+        <f t="shared" si="1"/>
+        <v>8700</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="2"/>
+        <v>-8700</v>
+      </c>
+      <c r="G54" s="4">
+        <f t="shared" si="3"/>
+        <v>-2969.6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="6">
+        <v>88</v>
+      </c>
+      <c r="B55" s="10">
+        <f t="shared" si="0"/>
+        <v>610</v>
+      </c>
+      <c r="C55" s="11">
+        <f t="shared" si="4"/>
+        <v>1787.109375</v>
+      </c>
+      <c r="D55" s="10">
+        <f t="shared" si="1"/>
+        <v>8800</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="2"/>
+        <v>-8800</v>
+      </c>
+      <c r="G55" s="4">
+        <f t="shared" si="3"/>
+        <v>-3003.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="6">
+        <v>89</v>
+      </c>
+      <c r="B56" s="10">
+        <f t="shared" si="0"/>
+        <v>605</v>
+      </c>
+      <c r="C56" s="11">
+        <f t="shared" si="4"/>
+        <v>1772.4609375</v>
+      </c>
+      <c r="D56" s="10">
+        <f t="shared" si="1"/>
+        <v>8900</v>
+      </c>
+      <c r="F56">
+        <f t="shared" si="2"/>
+        <v>-8900</v>
+      </c>
+      <c r="G56" s="4">
+        <f t="shared" si="3"/>
+        <v>-3037.9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="6">
+        <v>90</v>
+      </c>
+      <c r="B57" s="10">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+      <c r="C57" s="11">
+        <f t="shared" si="4"/>
+        <v>1757.8125</v>
+      </c>
+      <c r="D57" s="10">
+        <f t="shared" si="1"/>
+        <v>9000</v>
+      </c>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6">
+        <f t="shared" si="2"/>
+        <v>-9000</v>
+      </c>
+      <c r="G57" s="9">
+        <f t="shared" si="3"/>
+        <v>-3072</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="6">
+        <v>91</v>
+      </c>
+      <c r="B58" s="10">
+        <f t="shared" si="0"/>
+        <v>594</v>
+      </c>
+      <c r="C58" s="11">
+        <f t="shared" si="4"/>
+        <v>1740.234375</v>
+      </c>
+      <c r="D58" s="10">
+        <f t="shared" si="1"/>
+        <v>9100</v>
+      </c>
+      <c r="F58">
+        <f t="shared" si="2"/>
+        <v>-9100</v>
+      </c>
+      <c r="G58" s="4">
+        <f t="shared" si="3"/>
+        <v>-3106.1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="6">
+        <v>92</v>
+      </c>
+      <c r="B59" s="10">
+        <f t="shared" si="0"/>
+        <v>589</v>
+      </c>
+      <c r="C59" s="11">
+        <f t="shared" si="4"/>
+        <v>1725.5859375</v>
+      </c>
+      <c r="D59" s="10">
+        <f t="shared" si="1"/>
+        <v>9200</v>
+      </c>
+      <c r="F59">
+        <f t="shared" si="2"/>
+        <v>-9200</v>
+      </c>
+      <c r="G59" s="4">
+        <f t="shared" si="3"/>
+        <v>-3140.3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" s="6">
+        <v>93</v>
+      </c>
+      <c r="B60" s="10">
+        <f t="shared" si="0"/>
+        <v>584</v>
+      </c>
+      <c r="C60" s="11">
+        <f t="shared" si="4"/>
+        <v>1710.9375</v>
+      </c>
+      <c r="D60" s="10">
+        <f t="shared" si="1"/>
+        <v>9300</v>
+      </c>
+      <c r="F60">
+        <f t="shared" si="2"/>
+        <v>-9300</v>
+      </c>
+      <c r="G60" s="4">
+        <f t="shared" si="3"/>
+        <v>-3174.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" s="6">
+        <v>94</v>
+      </c>
+      <c r="B61" s="10">
+        <f t="shared" si="0"/>
+        <v>578</v>
+      </c>
+      <c r="C61" s="11">
+        <f t="shared" si="4"/>
+        <v>1693.359375</v>
+      </c>
+      <c r="D61" s="10">
+        <f t="shared" si="1"/>
+        <v>9400</v>
+      </c>
+      <c r="F61">
+        <f t="shared" si="2"/>
+        <v>-9400</v>
+      </c>
+      <c r="G61" s="4">
+        <f t="shared" si="3"/>
+        <v>-3208.5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>95</v>
+      </c>
+      <c r="B62" s="10">
+        <f t="shared" si="0"/>
+        <v>573</v>
+      </c>
+      <c r="C62" s="11">
+        <f t="shared" si="4"/>
+        <v>1678.7109375</v>
+      </c>
+      <c r="D62" s="10">
+        <f t="shared" si="1"/>
+        <v>9500</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="2"/>
+        <v>-9500</v>
+      </c>
+      <c r="G62" s="4">
+        <f t="shared" si="3"/>
+        <v>-3242.7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>96</v>
+      </c>
+      <c r="B63" s="10">
+        <f t="shared" si="0"/>
+        <v>568</v>
+      </c>
+      <c r="C63" s="11">
+        <f t="shared" si="4"/>
+        <v>1664.0625</v>
+      </c>
+      <c r="D63" s="10">
+        <f t="shared" si="1"/>
+        <v>9600</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="2"/>
+        <v>-9600</v>
+      </c>
+      <c r="G63" s="4">
+        <f t="shared" si="3"/>
+        <v>-3276.8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>97</v>
+      </c>
+      <c r="B64" s="10">
+        <f t="shared" si="0"/>
+        <v>562</v>
+      </c>
+      <c r="C64" s="11">
+        <f t="shared" si="4"/>
+        <v>1646.484375</v>
+      </c>
+      <c r="D64" s="10">
+        <f t="shared" si="1"/>
+        <v>9700</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="2"/>
+        <v>-9700</v>
+      </c>
+      <c r="G64" s="4">
+        <f t="shared" si="3"/>
+        <v>-3310.9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>98</v>
+      </c>
+      <c r="B65" s="10">
+        <f t="shared" si="0"/>
+        <v>557</v>
+      </c>
+      <c r="C65" s="11">
+        <f t="shared" si="4"/>
+        <v>1631.8359375</v>
+      </c>
+      <c r="D65" s="10">
+        <f t="shared" si="1"/>
+        <v>9800</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="2"/>
+        <v>-9800</v>
+      </c>
+      <c r="G65" s="4">
+        <f t="shared" si="3"/>
+        <v>-3345.1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>99</v>
+      </c>
+      <c r="B66" s="10">
+        <f t="shared" si="0"/>
+        <v>552</v>
+      </c>
+      <c r="C66" s="11">
+        <f t="shared" si="4"/>
+        <v>1617.1875</v>
+      </c>
+      <c r="D66" s="10">
+        <f t="shared" si="1"/>
+        <v>9900</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="2"/>
+        <v>-9900</v>
+      </c>
+      <c r="G66" s="4">
+        <f t="shared" si="3"/>
+        <v>-3379.2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>100</v>
+      </c>
+      <c r="B67" s="10">
+        <f t="shared" si="0"/>
+        <v>546</v>
+      </c>
+      <c r="C67" s="11">
+        <f t="shared" si="4"/>
+        <v>1599.609375</v>
+      </c>
+      <c r="D67" s="10">
+        <f t="shared" si="1"/>
+        <v>10000</v>
+      </c>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6">
+        <f t="shared" si="2"/>
+        <v>-10000</v>
+      </c>
+      <c r="G67" s="9">
+        <f t="shared" si="3"/>
+        <v>-3413.3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>101</v>
+      </c>
+      <c r="B68" s="10">
+        <f t="shared" si="0"/>
+        <v>541</v>
+      </c>
+      <c r="C68" s="11">
+        <f t="shared" si="4"/>
+        <v>1584.9609375</v>
+      </c>
+      <c r="D68" s="10">
+        <f t="shared" si="1"/>
+        <v>10100</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="2"/>
+        <v>-10100</v>
+      </c>
+      <c r="G68" s="4">
+        <f t="shared" si="3"/>
+        <v>-3447.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>102</v>
+      </c>
+      <c r="B69" s="10">
+        <f t="shared" si="0"/>
+        <v>536</v>
+      </c>
+      <c r="C69" s="11">
+        <f t="shared" si="4"/>
+        <v>1570.3125</v>
+      </c>
+      <c r="D69" s="10">
+        <f t="shared" si="1"/>
+        <v>10200</v>
+      </c>
+      <c r="F69">
+        <f t="shared" si="2"/>
+        <v>-10200</v>
+      </c>
+      <c r="G69" s="4">
+        <f t="shared" si="3"/>
+        <v>-3481.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>103</v>
+      </c>
+      <c r="B70" s="10">
+        <f t="shared" si="0"/>
+        <v>530</v>
+      </c>
+      <c r="C70" s="11">
+        <f t="shared" si="4"/>
+        <v>1552.734375</v>
+      </c>
+      <c r="D70" s="10">
+        <f t="shared" si="1"/>
+        <v>10300</v>
+      </c>
+      <c r="F70">
+        <f t="shared" si="2"/>
+        <v>-10300</v>
+      </c>
+      <c r="G70" s="4">
+        <f t="shared" si="3"/>
+        <v>-3515.7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>104</v>
+      </c>
+      <c r="B71" s="10">
+        <f t="shared" ref="B71:B134" si="5">ROUND($E$4-(((A71-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
+        <v>525</v>
+      </c>
+      <c r="C71" s="11">
+        <f t="shared" si="4"/>
+        <v>1538.0859375</v>
+      </c>
+      <c r="D71" s="10">
+        <f t="shared" si="1"/>
+        <v>10400</v>
+      </c>
+      <c r="F71">
+        <f t="shared" si="2"/>
+        <v>-10400</v>
+      </c>
+      <c r="G71" s="4">
+        <f t="shared" si="3"/>
+        <v>-3549.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>105</v>
+      </c>
+      <c r="B72" s="10">
+        <f t="shared" si="5"/>
+        <v>520</v>
+      </c>
+      <c r="C72" s="11">
+        <f t="shared" si="4"/>
+        <v>1523.4375</v>
+      </c>
+      <c r="D72" s="10">
+        <f t="shared" ref="D72:D87" si="6">A72*100</f>
+        <v>10500</v>
+      </c>
+      <c r="F72">
+        <f t="shared" ref="F72:F82" si="7">E72-D72</f>
+        <v>-10500</v>
+      </c>
+      <c r="G72" s="4">
+        <f t="shared" ref="G72:G82" si="8">ROUND(F72/$I$2,1)</f>
+        <v>-3584</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>106</v>
+      </c>
+      <c r="B73" s="10">
+        <f t="shared" si="5"/>
+        <v>514</v>
+      </c>
+      <c r="C73" s="11">
+        <f t="shared" ref="C73:C87" si="9">B73*$E$1/$E$2</f>
+        <v>1505.859375</v>
+      </c>
+      <c r="D73" s="10">
+        <f t="shared" si="6"/>
+        <v>10600</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="7"/>
+        <v>-10600</v>
+      </c>
+      <c r="G73" s="4">
+        <f t="shared" si="8"/>
+        <v>-3618.1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>107</v>
+      </c>
+      <c r="B74" s="10">
+        <f t="shared" si="5"/>
+        <v>509</v>
+      </c>
+      <c r="C74" s="11">
+        <f t="shared" si="9"/>
+        <v>1491.2109375</v>
+      </c>
+      <c r="D74" s="10">
+        <f t="shared" si="6"/>
+        <v>10700</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="7"/>
+        <v>-10700</v>
+      </c>
+      <c r="G74" s="4">
+        <f t="shared" si="8"/>
+        <v>-3652.3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>108</v>
+      </c>
+      <c r="B75" s="10">
+        <f t="shared" si="5"/>
+        <v>504</v>
+      </c>
+      <c r="C75" s="11">
+        <f t="shared" si="9"/>
+        <v>1476.5625</v>
+      </c>
+      <c r="D75" s="10">
+        <f t="shared" si="6"/>
+        <v>10800</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="7"/>
+        <v>-10800</v>
+      </c>
+      <c r="G75" s="4">
+        <f t="shared" si="8"/>
+        <v>-3686.4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>109</v>
+      </c>
+      <c r="B76" s="10">
+        <f t="shared" si="5"/>
+        <v>498</v>
+      </c>
+      <c r="C76" s="11">
+        <f t="shared" si="9"/>
+        <v>1458.984375</v>
+      </c>
+      <c r="D76" s="10">
+        <f t="shared" si="6"/>
+        <v>10900</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="7"/>
+        <v>-10900</v>
+      </c>
+      <c r="G76" s="4">
+        <f t="shared" si="8"/>
+        <v>-3720.5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>110</v>
+      </c>
+      <c r="B77" s="10">
+        <f t="shared" si="5"/>
+        <v>493</v>
+      </c>
+      <c r="C77" s="11">
+        <f t="shared" si="9"/>
+        <v>1444.3359375</v>
+      </c>
+      <c r="D77" s="10">
+        <f t="shared" si="6"/>
+        <v>11000</v>
+      </c>
+      <c r="E77" s="6"/>
+      <c r="F77" s="6">
+        <f t="shared" si="7"/>
+        <v>-11000</v>
+      </c>
+      <c r="G77" s="9">
+        <f t="shared" si="8"/>
+        <v>-3754.7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>111</v>
+      </c>
+      <c r="B78" s="10">
+        <f t="shared" si="5"/>
+        <v>488</v>
+      </c>
+      <c r="C78" s="11">
+        <f t="shared" si="9"/>
+        <v>1429.6875</v>
+      </c>
+      <c r="D78" s="10">
+        <f t="shared" si="6"/>
+        <v>11100</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="7"/>
+        <v>-11100</v>
+      </c>
+      <c r="G78" s="4">
+        <f t="shared" si="8"/>
+        <v>-3788.8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>112</v>
+      </c>
+      <c r="B79" s="10">
+        <f t="shared" si="5"/>
+        <v>482</v>
+      </c>
+      <c r="C79" s="11">
+        <f t="shared" si="9"/>
+        <v>1412.109375</v>
+      </c>
+      <c r="D79" s="10">
+        <f t="shared" si="6"/>
+        <v>11200</v>
+      </c>
+      <c r="E79" s="6"/>
+      <c r="F79" s="6">
+        <f t="shared" si="7"/>
+        <v>-11200</v>
+      </c>
+      <c r="G79" s="9">
+        <f t="shared" si="8"/>
+        <v>-3822.9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>113</v>
+      </c>
+      <c r="B80" s="10">
+        <f t="shared" si="5"/>
+        <v>477</v>
+      </c>
+      <c r="C80" s="11">
+        <f t="shared" si="9"/>
+        <v>1397.4609375</v>
+      </c>
+      <c r="D80" s="10">
+        <f t="shared" si="6"/>
+        <v>11300</v>
+      </c>
+      <c r="F80">
+        <f t="shared" si="7"/>
+        <v>-11300</v>
+      </c>
+      <c r="G80" s="4">
+        <f t="shared" si="8"/>
+        <v>-3857.1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>114</v>
+      </c>
+      <c r="B81" s="10">
+        <f t="shared" si="5"/>
+        <v>471</v>
+      </c>
+      <c r="C81" s="11">
+        <f t="shared" si="9"/>
+        <v>1379.8828125</v>
+      </c>
+      <c r="D81" s="10">
+        <f t="shared" si="6"/>
+        <v>11400</v>
+      </c>
+      <c r="E81" s="6"/>
+      <c r="F81" s="6">
+        <f t="shared" si="7"/>
+        <v>-11400</v>
+      </c>
+      <c r="G81" s="9">
+        <f t="shared" si="8"/>
+        <v>-3891.2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>115</v>
+      </c>
+      <c r="B82" s="10">
+        <f t="shared" si="5"/>
+        <v>466</v>
+      </c>
+      <c r="C82" s="11">
+        <f t="shared" si="9"/>
+        <v>1365.234375</v>
+      </c>
+      <c r="D82" s="10">
+        <f t="shared" si="6"/>
+        <v>11500</v>
+      </c>
+      <c r="F82">
+        <f t="shared" si="7"/>
+        <v>-11500</v>
+      </c>
+      <c r="G82" s="4">
+        <f t="shared" si="8"/>
+        <v>-3925.3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>116</v>
+      </c>
+      <c r="B83" s="10">
+        <f t="shared" si="5"/>
+        <v>461</v>
+      </c>
+      <c r="C83" s="11">
+        <f t="shared" si="9"/>
+        <v>1350.5859375</v>
+      </c>
+      <c r="D83" s="10">
+        <f t="shared" si="6"/>
+        <v>11600</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>117</v>
+      </c>
+      <c r="B84" s="10">
+        <f t="shared" si="5"/>
+        <v>455</v>
+      </c>
+      <c r="C84" s="11">
+        <f t="shared" si="9"/>
+        <v>1333.0078125</v>
+      </c>
+      <c r="D84" s="10">
+        <f t="shared" si="6"/>
+        <v>11700</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>118</v>
+      </c>
+      <c r="B85" s="10">
+        <f t="shared" si="5"/>
+        <v>450</v>
+      </c>
+      <c r="C85" s="11">
+        <f t="shared" si="9"/>
+        <v>1318.359375</v>
+      </c>
+      <c r="D85" s="10">
+        <f t="shared" si="6"/>
+        <v>11800</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>119</v>
+      </c>
+      <c r="B86" s="10">
+        <f t="shared" si="5"/>
+        <v>445</v>
+      </c>
+      <c r="C86" s="11">
+        <f t="shared" si="9"/>
+        <v>1303.7109375</v>
+      </c>
+      <c r="D86" s="10">
+        <f t="shared" si="6"/>
+        <v>11900</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>120</v>
+      </c>
+      <c r="B87" s="10">
+        <f t="shared" si="5"/>
+        <v>439</v>
+      </c>
+      <c r="C87" s="11">
+        <f t="shared" si="9"/>
+        <v>1286.1328125</v>
+      </c>
+      <c r="D87" s="10">
+        <f t="shared" si="6"/>
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>121</v>
+      </c>
+      <c r="B88" s="10">
+        <f t="shared" ref="B88:B106" si="10">ROUND($E$4-(((A88-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
+        <v>434</v>
+      </c>
+      <c r="C88" s="11">
+        <f t="shared" ref="C88:C106" si="11">B88*$E$1/$E$2</f>
+        <v>1271.484375</v>
+      </c>
+      <c r="D88" s="10">
+        <f t="shared" ref="D88:D106" si="12">A88*100</f>
+        <v>12100</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>122</v>
+      </c>
+      <c r="B89" s="10">
+        <f t="shared" si="10"/>
+        <v>429</v>
+      </c>
+      <c r="C89" s="11">
+        <f t="shared" si="11"/>
+        <v>1256.8359375</v>
+      </c>
+      <c r="D89" s="10">
+        <f t="shared" si="12"/>
+        <v>12200</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>123</v>
+      </c>
+      <c r="B90" s="10">
+        <f t="shared" si="10"/>
+        <v>423</v>
+      </c>
+      <c r="C90" s="11">
+        <f t="shared" si="11"/>
+        <v>1239.2578125</v>
+      </c>
+      <c r="D90" s="10">
+        <f t="shared" si="12"/>
+        <v>12300</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>124</v>
+      </c>
+      <c r="B91" s="10">
+        <f t="shared" si="10"/>
+        <v>418</v>
+      </c>
+      <c r="C91" s="11">
+        <f t="shared" si="11"/>
+        <v>1224.609375</v>
+      </c>
+      <c r="D91" s="10">
+        <f t="shared" si="12"/>
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>125</v>
+      </c>
+      <c r="B92" s="10">
+        <f t="shared" si="10"/>
+        <v>413</v>
+      </c>
+      <c r="C92" s="11">
+        <f t="shared" si="11"/>
+        <v>1209.9609375</v>
+      </c>
+      <c r="D92" s="10">
+        <f t="shared" si="12"/>
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>126</v>
+      </c>
+      <c r="B93" s="10">
+        <f t="shared" si="10"/>
+        <v>407</v>
+      </c>
+      <c r="C93" s="11">
+        <f t="shared" si="11"/>
+        <v>1192.3828125</v>
+      </c>
+      <c r="D93" s="10">
+        <f t="shared" si="12"/>
+        <v>12600</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>127</v>
+      </c>
+      <c r="B94" s="10">
+        <f t="shared" si="10"/>
+        <v>402</v>
+      </c>
+      <c r="C94" s="11">
+        <f t="shared" si="11"/>
+        <v>1177.734375</v>
+      </c>
+      <c r="D94" s="10">
+        <f t="shared" si="12"/>
+        <v>12700</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>128</v>
+      </c>
+      <c r="B95" s="10">
+        <f t="shared" si="10"/>
+        <v>397</v>
+      </c>
+      <c r="C95" s="11">
+        <f t="shared" si="11"/>
+        <v>1163.0859375</v>
+      </c>
+      <c r="D95" s="10">
+        <f t="shared" si="12"/>
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>129</v>
+      </c>
+      <c r="B96" s="10">
+        <f t="shared" si="10"/>
+        <v>391</v>
+      </c>
+      <c r="C96" s="11">
+        <f t="shared" si="11"/>
+        <v>1145.5078125</v>
+      </c>
+      <c r="D96" s="10">
+        <f t="shared" si="12"/>
+        <v>12900</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>130</v>
+      </c>
+      <c r="B97" s="10">
+        <f t="shared" si="10"/>
+        <v>386</v>
+      </c>
+      <c r="C97" s="11">
+        <f t="shared" si="11"/>
+        <v>1130.859375</v>
+      </c>
+      <c r="D97" s="10">
+        <f t="shared" si="12"/>
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>131</v>
+      </c>
+      <c r="B98" s="10">
+        <f t="shared" si="10"/>
+        <v>381</v>
+      </c>
+      <c r="C98" s="11">
+        <f t="shared" si="11"/>
+        <v>1116.2109375</v>
+      </c>
+      <c r="D98" s="10">
+        <f t="shared" si="12"/>
+        <v>13100</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>132</v>
+      </c>
+      <c r="B99" s="10">
+        <f t="shared" si="10"/>
+        <v>375</v>
+      </c>
+      <c r="C99" s="11">
+        <f t="shared" si="11"/>
+        <v>1098.6328125</v>
+      </c>
+      <c r="D99" s="10">
+        <f t="shared" si="12"/>
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>133</v>
+      </c>
+      <c r="B100" s="10">
+        <f t="shared" si="10"/>
+        <v>370</v>
+      </c>
+      <c r="C100" s="11">
+        <f t="shared" si="11"/>
+        <v>1083.984375</v>
+      </c>
+      <c r="D100" s="10">
+        <f t="shared" si="12"/>
+        <v>13300</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>134</v>
+      </c>
+      <c r="B101" s="10">
+        <f t="shared" si="10"/>
+        <v>365</v>
+      </c>
+      <c r="C101" s="11">
+        <f t="shared" si="11"/>
+        <v>1069.3359375</v>
+      </c>
+      <c r="D101" s="10">
+        <f t="shared" si="12"/>
+        <v>13400</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>135</v>
+      </c>
+      <c r="B102" s="10">
+        <f t="shared" si="10"/>
+        <v>359</v>
+      </c>
+      <c r="C102" s="11">
+        <f t="shared" si="11"/>
+        <v>1051.7578125</v>
+      </c>
+      <c r="D102" s="10">
+        <f t="shared" si="12"/>
+        <v>13500</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>136</v>
+      </c>
+      <c r="B103" s="10">
+        <f t="shared" si="10"/>
+        <v>354</v>
+      </c>
+      <c r="C103" s="11">
+        <f t="shared" si="11"/>
+        <v>1037.109375</v>
+      </c>
+      <c r="D103" s="10">
+        <f t="shared" si="12"/>
+        <v>13600</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>137</v>
+      </c>
+      <c r="B104" s="10">
+        <f t="shared" si="10"/>
+        <v>349</v>
+      </c>
+      <c r="C104" s="11">
+        <f t="shared" si="11"/>
+        <v>1022.4609375</v>
+      </c>
+      <c r="D104" s="10">
+        <f t="shared" si="12"/>
+        <v>13700</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>138</v>
+      </c>
+      <c r="B105" s="10">
+        <f t="shared" si="10"/>
+        <v>343</v>
+      </c>
+      <c r="C105" s="11">
+        <f t="shared" si="11"/>
+        <v>1004.8828125</v>
+      </c>
+      <c r="D105" s="10">
+        <f t="shared" si="12"/>
+        <v>13800</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>139</v>
+      </c>
+      <c r="B106" s="10">
+        <f t="shared" si="10"/>
+        <v>338</v>
+      </c>
+      <c r="C106" s="11">
+        <f t="shared" si="11"/>
+        <v>990.234375</v>
+      </c>
+      <c r="D106" s="10">
+        <f t="shared" si="12"/>
+        <v>13900</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>140</v>
+      </c>
+      <c r="B107" s="10">
+        <f t="shared" ref="B107:B152" si="13">ROUND($E$4-(((A107-$B$2)*($E$4-$E$3))/($B$1-$B$2)),0)</f>
+        <v>333</v>
+      </c>
+      <c r="C107" s="11">
+        <f t="shared" ref="C107:C152" si="14">B107*$E$1/$E$2</f>
+        <v>975.5859375</v>
+      </c>
+      <c r="D107" s="10">
+        <f t="shared" ref="D107:D152" si="15">A107*100</f>
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>141</v>
+      </c>
+      <c r="B108" s="10">
+        <f t="shared" si="13"/>
+        <v>327</v>
+      </c>
+      <c r="C108" s="11">
+        <f t="shared" si="14"/>
+        <v>958.0078125</v>
+      </c>
+      <c r="D108" s="10">
+        <f t="shared" si="15"/>
+        <v>14100</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>142</v>
+      </c>
+      <c r="B109" s="10">
+        <f t="shared" si="13"/>
+        <v>322</v>
+      </c>
+      <c r="C109" s="11">
+        <f t="shared" si="14"/>
+        <v>943.359375</v>
+      </c>
+      <c r="D109" s="10">
+        <f t="shared" si="15"/>
+        <v>14200</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A110" s="6">
+        <v>143</v>
+      </c>
+      <c r="B110" s="10">
+        <f t="shared" si="13"/>
+        <v>316</v>
+      </c>
+      <c r="C110" s="11">
+        <f t="shared" si="14"/>
+        <v>925.78125</v>
+      </c>
+      <c r="D110" s="10">
+        <f t="shared" si="15"/>
+        <v>14300</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A111" s="6">
+        <v>144</v>
+      </c>
+      <c r="B111" s="10">
+        <f t="shared" si="13"/>
+        <v>311</v>
+      </c>
+      <c r="C111" s="11">
+        <f t="shared" si="14"/>
+        <v>911.1328125</v>
+      </c>
+      <c r="D111" s="10">
+        <f t="shared" si="15"/>
+        <v>14400</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A112" s="6">
+        <v>145</v>
+      </c>
+      <c r="B112" s="10">
+        <f t="shared" si="13"/>
+        <v>306</v>
+      </c>
+      <c r="C112" s="11">
+        <f t="shared" si="14"/>
+        <v>896.484375</v>
+      </c>
+      <c r="D112" s="10">
+        <f t="shared" si="15"/>
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" s="6">
+        <v>146</v>
+      </c>
+      <c r="B113" s="10">
+        <f t="shared" si="13"/>
+        <v>300</v>
+      </c>
+      <c r="C113" s="11">
+        <f t="shared" si="14"/>
+        <v>878.90625</v>
+      </c>
+      <c r="D113" s="10">
+        <f t="shared" si="15"/>
+        <v>14600</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A114" s="6">
+        <v>147</v>
+      </c>
+      <c r="B114" s="10">
+        <f t="shared" si="13"/>
+        <v>295</v>
+      </c>
+      <c r="C114" s="11">
+        <f t="shared" si="14"/>
+        <v>864.2578125</v>
+      </c>
+      <c r="D114" s="10">
+        <f t="shared" si="15"/>
+        <v>14700</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A115" s="6">
+        <v>148</v>
+      </c>
+      <c r="B115" s="10">
+        <f t="shared" si="13"/>
+        <v>290</v>
+      </c>
+      <c r="C115" s="11">
+        <f t="shared" si="14"/>
+        <v>849.609375</v>
+      </c>
+      <c r="D115" s="10">
+        <f t="shared" si="15"/>
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A116" s="6">
+        <v>149</v>
+      </c>
+      <c r="B116" s="10">
+        <f t="shared" si="13"/>
+        <v>284</v>
+      </c>
+      <c r="C116" s="11">
+        <f t="shared" si="14"/>
+        <v>832.03125</v>
+      </c>
+      <c r="D116" s="10">
+        <f t="shared" si="15"/>
+        <v>14900</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A117" s="6">
+        <v>150</v>
+      </c>
+      <c r="B117" s="10">
+        <f t="shared" si="13"/>
+        <v>279</v>
+      </c>
+      <c r="C117" s="11">
+        <f t="shared" si="14"/>
+        <v>817.3828125</v>
+      </c>
+      <c r="D117" s="10">
+        <f t="shared" si="15"/>
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A118" s="6">
+        <v>151</v>
+      </c>
+      <c r="B118" s="10">
+        <f t="shared" si="13"/>
+        <v>274</v>
+      </c>
+      <c r="C118" s="11">
+        <f t="shared" si="14"/>
+        <v>802.734375</v>
+      </c>
+      <c r="D118" s="10">
+        <f t="shared" si="15"/>
+        <v>15100</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A119" s="6">
+        <v>152</v>
+      </c>
+      <c r="B119" s="10">
+        <f t="shared" si="13"/>
+        <v>268</v>
+      </c>
+      <c r="C119" s="11">
+        <f t="shared" si="14"/>
+        <v>785.15625</v>
+      </c>
+      <c r="D119" s="10">
+        <f t="shared" si="15"/>
+        <v>15200</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A120" s="6">
+        <v>153</v>
+      </c>
+      <c r="B120" s="10">
+        <f t="shared" si="13"/>
+        <v>263</v>
+      </c>
+      <c r="C120" s="11">
+        <f t="shared" si="14"/>
+        <v>770.5078125</v>
+      </c>
+      <c r="D120" s="10">
+        <f t="shared" si="15"/>
+        <v>15300</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>154</v>
+      </c>
+      <c r="B121" s="10">
+        <f t="shared" si="13"/>
+        <v>258</v>
+      </c>
+      <c r="C121" s="11">
+        <f t="shared" si="14"/>
+        <v>755.859375</v>
+      </c>
+      <c r="D121" s="10">
+        <f t="shared" si="15"/>
+        <v>15400</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A122" s="6">
+        <v>155</v>
+      </c>
+      <c r="B122" s="10">
+        <f t="shared" si="13"/>
+        <v>252</v>
+      </c>
+      <c r="C122" s="11">
+        <f t="shared" si="14"/>
+        <v>738.28125</v>
+      </c>
+      <c r="D122" s="10">
+        <f t="shared" si="15"/>
+        <v>15500</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A123" s="6">
+        <v>156</v>
+      </c>
+      <c r="B123" s="10">
+        <f t="shared" si="13"/>
+        <v>247</v>
+      </c>
+      <c r="C123" s="11">
+        <f t="shared" si="14"/>
+        <v>723.6328125</v>
+      </c>
+      <c r="D123" s="10">
+        <f t="shared" si="15"/>
+        <v>15600</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A124" s="6">
+        <v>157</v>
+      </c>
+      <c r="B124" s="10">
+        <f t="shared" si="13"/>
+        <v>242</v>
+      </c>
+      <c r="C124" s="11">
+        <f t="shared" si="14"/>
+        <v>708.984375</v>
+      </c>
+      <c r="D124" s="10">
+        <f t="shared" si="15"/>
+        <v>15700</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A125" s="6">
+        <v>158</v>
+      </c>
+      <c r="B125" s="10">
+        <f t="shared" si="13"/>
+        <v>236</v>
+      </c>
+      <c r="C125" s="11">
+        <f t="shared" si="14"/>
+        <v>691.40625</v>
+      </c>
+      <c r="D125" s="10">
+        <f t="shared" si="15"/>
+        <v>15800</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A126" s="6">
+        <v>159</v>
+      </c>
+      <c r="B126" s="10">
+        <f t="shared" si="13"/>
+        <v>231</v>
+      </c>
+      <c r="C126" s="11">
+        <f t="shared" si="14"/>
+        <v>676.7578125</v>
+      </c>
+      <c r="D126" s="10">
+        <f t="shared" si="15"/>
+        <v>15900</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A127" s="6">
+        <v>160</v>
+      </c>
+      <c r="B127" s="10">
+        <f t="shared" si="13"/>
+        <v>226</v>
+      </c>
+      <c r="C127" s="11">
+        <f t="shared" si="14"/>
+        <v>662.109375</v>
+      </c>
+      <c r="D127" s="10">
+        <f t="shared" si="15"/>
+        <v>16000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A128" s="6">
+        <v>161</v>
+      </c>
+      <c r="B128" s="10">
+        <f t="shared" si="13"/>
+        <v>220</v>
+      </c>
+      <c r="C128" s="11">
+        <f t="shared" si="14"/>
+        <v>644.53125</v>
+      </c>
+      <c r="D128" s="10">
+        <f t="shared" si="15"/>
+        <v>16100</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A129" s="6">
+        <v>162</v>
+      </c>
+      <c r="B129" s="10">
+        <f t="shared" si="13"/>
+        <v>215</v>
+      </c>
+      <c r="C129" s="11">
+        <f t="shared" si="14"/>
+        <v>629.8828125</v>
+      </c>
+      <c r="D129" s="10">
+        <f t="shared" si="15"/>
+        <v>16200</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A130" s="6">
+        <v>163</v>
+      </c>
+      <c r="B130" s="10">
+        <f t="shared" si="13"/>
+        <v>210</v>
+      </c>
+      <c r="C130" s="11">
+        <f t="shared" si="14"/>
+        <v>615.234375</v>
+      </c>
+      <c r="D130" s="10">
+        <f t="shared" si="15"/>
+        <v>16300</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A131" s="6">
+        <v>164</v>
+      </c>
+      <c r="B131" s="10">
+        <f t="shared" si="13"/>
+        <v>204</v>
+      </c>
+      <c r="C131" s="11">
+        <f t="shared" si="14"/>
+        <v>597.65625</v>
+      </c>
+      <c r="D131" s="10">
+        <f t="shared" si="15"/>
+        <v>16400</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="6">
+        <v>165</v>
+      </c>
+      <c r="B132" s="10">
+        <f t="shared" si="13"/>
+        <v>199</v>
+      </c>
+      <c r="C132" s="11">
+        <f t="shared" si="14"/>
+        <v>583.0078125</v>
+      </c>
+      <c r="D132" s="10">
+        <f t="shared" si="15"/>
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A133" s="6">
+        <v>166</v>
+      </c>
+      <c r="B133" s="10">
+        <f t="shared" si="13"/>
+        <v>194</v>
+      </c>
+      <c r="C133" s="11">
+        <f t="shared" si="14"/>
+        <v>568.359375</v>
+      </c>
+      <c r="D133" s="10">
+        <f t="shared" si="15"/>
+        <v>16600</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A134" s="6">
+        <v>167</v>
+      </c>
+      <c r="B134" s="10">
+        <f t="shared" si="13"/>
+        <v>188</v>
+      </c>
+      <c r="C134" s="11">
+        <f t="shared" si="14"/>
+        <v>550.78125</v>
+      </c>
+      <c r="D134" s="10">
+        <f t="shared" si="15"/>
+        <v>16700</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A135" s="6">
+        <v>168</v>
+      </c>
+      <c r="B135" s="10">
+        <f t="shared" si="13"/>
+        <v>183</v>
+      </c>
+      <c r="C135" s="11">
+        <f t="shared" si="14"/>
+        <v>536.1328125</v>
+      </c>
+      <c r="D135" s="10">
+        <f t="shared" si="15"/>
+        <v>16800</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A136" s="6">
+        <v>169</v>
+      </c>
+      <c r="B136" s="10">
+        <f t="shared" si="13"/>
+        <v>178</v>
+      </c>
+      <c r="C136" s="11">
+        <f t="shared" si="14"/>
+        <v>521.484375</v>
+      </c>
+      <c r="D136" s="10">
+        <f t="shared" si="15"/>
+        <v>16900</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A137" s="6">
+        <v>170</v>
+      </c>
+      <c r="B137" s="10">
+        <f t="shared" si="13"/>
+        <v>172</v>
+      </c>
+      <c r="C137" s="11">
+        <f t="shared" si="14"/>
+        <v>503.90625</v>
+      </c>
+      <c r="D137" s="10">
+        <f t="shared" si="15"/>
+        <v>17000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A138" s="6">
+        <v>171</v>
+      </c>
+      <c r="B138" s="10">
+        <f t="shared" si="13"/>
+        <v>167</v>
+      </c>
+      <c r="C138" s="11">
+        <f t="shared" si="14"/>
+        <v>489.2578125</v>
+      </c>
+      <c r="D138" s="10">
+        <f t="shared" si="15"/>
+        <v>17100</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A139" s="6">
+        <v>172</v>
+      </c>
+      <c r="B139" s="10">
+        <f t="shared" si="13"/>
+        <v>161</v>
+      </c>
+      <c r="C139" s="11">
+        <f t="shared" si="14"/>
+        <v>471.6796875</v>
+      </c>
+      <c r="D139" s="10">
+        <f t="shared" si="15"/>
+        <v>17200</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A140" s="6">
+        <v>173</v>
+      </c>
+      <c r="B140" s="10">
+        <f t="shared" si="13"/>
+        <v>156</v>
+      </c>
+      <c r="C140" s="11">
+        <f t="shared" si="14"/>
+        <v>457.03125</v>
+      </c>
+      <c r="D140" s="10">
+        <f t="shared" si="15"/>
+        <v>17300</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A141" s="6">
+        <v>174</v>
+      </c>
+      <c r="B141" s="10">
+        <f t="shared" si="13"/>
+        <v>151</v>
+      </c>
+      <c r="C141" s="11">
+        <f t="shared" si="14"/>
+        <v>442.3828125</v>
+      </c>
+      <c r="D141" s="10">
+        <f t="shared" si="15"/>
+        <v>17400</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="6">
+        <v>175</v>
+      </c>
+      <c r="B142" s="10">
+        <f t="shared" si="13"/>
+        <v>145</v>
+      </c>
+      <c r="C142" s="11">
+        <f t="shared" si="14"/>
+        <v>424.8046875</v>
+      </c>
+      <c r="D142" s="10">
+        <f t="shared" si="15"/>
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A143" s="6">
+        <v>176</v>
+      </c>
+      <c r="B143" s="10">
+        <f t="shared" si="13"/>
+        <v>140</v>
+      </c>
+      <c r="C143" s="11">
+        <f t="shared" si="14"/>
+        <v>410.15625</v>
+      </c>
+      <c r="D143" s="10">
+        <f t="shared" si="15"/>
+        <v>17600</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A144" s="6">
+        <v>177</v>
+      </c>
+      <c r="B144" s="10">
+        <f t="shared" si="13"/>
+        <v>135</v>
+      </c>
+      <c r="C144" s="11">
+        <f t="shared" si="14"/>
+        <v>395.5078125</v>
+      </c>
+      <c r="D144" s="10">
+        <f t="shared" si="15"/>
+        <v>17700</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A145" s="6">
+        <v>178</v>
+      </c>
+      <c r="B145" s="10">
+        <f t="shared" si="13"/>
+        <v>129</v>
+      </c>
+      <c r="C145" s="11">
+        <f t="shared" si="14"/>
+        <v>377.9296875</v>
+      </c>
+      <c r="D145" s="10">
+        <f t="shared" si="15"/>
+        <v>17800</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A146" s="6">
+        <v>179</v>
+      </c>
+      <c r="B146" s="10">
+        <f t="shared" si="13"/>
+        <v>124</v>
+      </c>
+      <c r="C146" s="11">
+        <f t="shared" si="14"/>
+        <v>363.28125</v>
+      </c>
+      <c r="D146" s="10">
+        <f t="shared" si="15"/>
+        <v>17900</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A147" s="6">
+        <v>180</v>
+      </c>
+      <c r="B147" s="10">
+        <f t="shared" si="13"/>
+        <v>119</v>
+      </c>
+      <c r="C147" s="11">
+        <f t="shared" si="14"/>
+        <v>348.6328125</v>
+      </c>
+      <c r="D147" s="10">
+        <f t="shared" si="15"/>
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A148" s="6">
+        <v>181</v>
+      </c>
+      <c r="B148" s="10">
+        <f t="shared" si="13"/>
+        <v>113</v>
+      </c>
+      <c r="C148" s="11">
+        <f t="shared" si="14"/>
+        <v>331.0546875</v>
+      </c>
+      <c r="D148" s="10">
+        <f t="shared" si="15"/>
+        <v>18100</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A149" s="6">
+        <v>182</v>
+      </c>
+      <c r="B149" s="10">
+        <f t="shared" si="13"/>
+        <v>108</v>
+      </c>
+      <c r="C149" s="11">
+        <f t="shared" si="14"/>
+        <v>316.40625</v>
+      </c>
+      <c r="D149" s="10">
+        <f t="shared" si="15"/>
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A150" s="6">
+        <v>183</v>
+      </c>
+      <c r="B150" s="10">
+        <f t="shared" si="13"/>
+        <v>103</v>
+      </c>
+      <c r="C150" s="11">
+        <f t="shared" si="14"/>
+        <v>301.7578125</v>
+      </c>
+      <c r="D150" s="10">
+        <f t="shared" si="15"/>
+        <v>18300</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A151" s="6">
+        <v>184</v>
+      </c>
+      <c r="B151" s="10">
+        <f t="shared" si="13"/>
+        <v>97</v>
+      </c>
+      <c r="C151" s="11">
+        <f t="shared" si="14"/>
+        <v>284.1796875</v>
+      </c>
+      <c r="D151" s="10">
+        <f t="shared" si="15"/>
+        <v>18400</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>185</v>
+      </c>
+      <c r="B152" s="10">
+        <f t="shared" si="13"/>
+        <v>92</v>
+      </c>
+      <c r="C152" s="11">
+        <f t="shared" si="14"/>
+        <v>269.53125</v>
+      </c>
+      <c r="D152" s="10">
+        <f t="shared" si="15"/>
+        <v>18500</v>
       </c>
     </row>
   </sheetData>
